--- a/IROC_2025/Code/IROC_2025_DataContributors.xlsx
+++ b/IROC_2025/Code/IROC_2025_DataContributors.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="1845">
   <si>
     <t>Region</t>
   </si>
@@ -1711,6 +1711,3798 @@
   </si>
   <si>
     <t>Solveig R. Olafsdottir (solveig.rosa.olafsdottir@hafogvatn.is)</t>
+  </si>
+  <si>
+    <t>Pascal Morin (pmorin@sb-roscoff.fr)</t>
+  </si>
+  <si>
+    <t>Eoghan Daly (eoghan.daly@marine.ie)</t>
+  </si>
+  <si>
+    <t>Billy Hunter (billy.hunter@afbini.gov.uk)</t>
+  </si>
+  <si>
+    <t>Inga Kirstein (inga.kirstein@awi.de)</t>
+  </si>
+  <si>
+    <t>Dagmar Kieke (dagmar.kieke@bsh.de)</t>
+  </si>
+  <si>
+    <t>Bee Berx &amp; Berit Rabe (MD.Oceanography@gov.scot)</t>
+  </si>
+  <si>
+    <t>Lianne Harrison (lianne.harrison@cefas.gov.uk)</t>
+  </si>
+  <si>
+    <t>Jon Albretsen (jon.albretsen@hi.no)</t>
+  </si>
+  <si>
+    <t>Tim J. Smyth (tjsm@pml.ac.uk)</t>
+  </si>
+  <si>
+    <t>Jon Albretsen (jon.albretsen@hi.no)</t>
+  </si>
+  <si>
+    <t>Bee Berx &amp; Berit Rabe (MD.Oceanography@gov.scot)</t>
+  </si>
+  <si>
+    <t>Johanna Linders (johanna.linders@smhi.se)</t>
+  </si>
+  <si>
+    <t>Tycjan Wodzinowski (twodzinowski@mir.gdynia.pl)</t>
+  </si>
+  <si>
+    <t>Johanna Linders (johanna.linders@smhi.se)</t>
+  </si>
+  <si>
+    <t>Antti Westerlund (antti.westerlund@fmi.fi)</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>BBAY</t>
+  </si>
+  <si>
+    <t>NEAS</t>
+  </si>
+  <si>
+    <t>SPNA</t>
+  </si>
+  <si>
+    <t>BICC</t>
+  </si>
+  <si>
+    <t>NSBS</t>
+  </si>
+  <si>
+    <t>NWES</t>
+  </si>
+  <si>
+    <t>BALT</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>BBAY_001</t>
+  </si>
+  <si>
+    <t>BBAY_002</t>
+  </si>
+  <si>
+    <t>BBAY_003</t>
+  </si>
+  <si>
+    <t>BBAY_004</t>
+  </si>
+  <si>
+    <t>BBAY_005</t>
+  </si>
+  <si>
+    <t>NEAS_001</t>
+  </si>
+  <si>
+    <t>NEAS_002</t>
+  </si>
+  <si>
+    <t>NEAS_003</t>
+  </si>
+  <si>
+    <t>NEAS_004</t>
+  </si>
+  <si>
+    <t>NEAS_005</t>
+  </si>
+  <si>
+    <t>NEAS_006</t>
+  </si>
+  <si>
+    <t>NEAS_007</t>
+  </si>
+  <si>
+    <t>NEAS_008</t>
+  </si>
+  <si>
+    <t>NEAS_009</t>
+  </si>
+  <si>
+    <t>NEAS_010</t>
+  </si>
+  <si>
+    <t>NEAS_011</t>
+  </si>
+  <si>
+    <t>NEAS_012</t>
+  </si>
+  <si>
+    <t>NEAS_013</t>
+  </si>
+  <si>
+    <t>NEAS_014</t>
+  </si>
+  <si>
+    <t>NEAS_015</t>
+  </si>
+  <si>
+    <t>NEAS_016</t>
+  </si>
+  <si>
+    <t>NEAS_017</t>
+  </si>
+  <si>
+    <t>NEAS_018</t>
+  </si>
+  <si>
+    <t>NEAS_019</t>
+  </si>
+  <si>
+    <t>NEAS_020</t>
+  </si>
+  <si>
+    <t>NEAS_021</t>
+  </si>
+  <si>
+    <t>SPNA_001</t>
+  </si>
+  <si>
+    <t>SPNA_002</t>
+  </si>
+  <si>
+    <t>SPNA_003</t>
+  </si>
+  <si>
+    <t>SPNA_004</t>
+  </si>
+  <si>
+    <t>SPNA_006</t>
+  </si>
+  <si>
+    <t>SPNA_007</t>
+  </si>
+  <si>
+    <t>SPNA_008</t>
+  </si>
+  <si>
+    <t>SPNA_017</t>
+  </si>
+  <si>
+    <t>SPNA_018</t>
+  </si>
+  <si>
+    <t>SPNA_019</t>
+  </si>
+  <si>
+    <t>SPNA_020</t>
+  </si>
+  <si>
+    <t>SPNA_021</t>
+  </si>
+  <si>
+    <t>SPNA_022</t>
+  </si>
+  <si>
+    <t>SPNA_023</t>
+  </si>
+  <si>
+    <t>SPNA_024</t>
+  </si>
+  <si>
+    <t>SPNA_025</t>
+  </si>
+  <si>
+    <t>SPNA_026</t>
+  </si>
+  <si>
+    <t>SPNA_027</t>
+  </si>
+  <si>
+    <t>SPNA_028</t>
+  </si>
+  <si>
+    <t>SPNA_029</t>
+  </si>
+  <si>
+    <t>BICC_003</t>
+  </si>
+  <si>
+    <t>BICC_004</t>
+  </si>
+  <si>
+    <t>BICC_005</t>
+  </si>
+  <si>
+    <t>BICC_006</t>
+  </si>
+  <si>
+    <t>BICC_007</t>
+  </si>
+  <si>
+    <t>BICC_008</t>
+  </si>
+  <si>
+    <t>BICC_009</t>
+  </si>
+  <si>
+    <t>BICC_010</t>
+  </si>
+  <si>
+    <t>BICC_011</t>
+  </si>
+  <si>
+    <t>BICC_012</t>
+  </si>
+  <si>
+    <t>BICC_013</t>
+  </si>
+  <si>
+    <t>BICC_014</t>
+  </si>
+  <si>
+    <t>BICC_015</t>
+  </si>
+  <si>
+    <t>BICC_016</t>
+  </si>
+  <si>
+    <t>BICC_017</t>
+  </si>
+  <si>
+    <t>BICC_018</t>
+  </si>
+  <si>
+    <t>BICC_110</t>
+  </si>
+  <si>
+    <t>NSBS_001</t>
+  </si>
+  <si>
+    <t>NSBS_002</t>
+  </si>
+  <si>
+    <t>NSBS_003</t>
+  </si>
+  <si>
+    <t>NSBS_004</t>
+  </si>
+  <si>
+    <t>NSBS_005</t>
+  </si>
+  <si>
+    <t>NSBS_006</t>
+  </si>
+  <si>
+    <t>NSBS_007</t>
+  </si>
+  <si>
+    <t>NSBS_008</t>
+  </si>
+  <si>
+    <t>NSBS_009</t>
+  </si>
+  <si>
+    <t>NSBS_010</t>
+  </si>
+  <si>
+    <t>NSBS_011</t>
+  </si>
+  <si>
+    <t>NSBS_012</t>
+  </si>
+  <si>
+    <t>NSBS_013</t>
+  </si>
+  <si>
+    <t>NSBS_014</t>
+  </si>
+  <si>
+    <t>NSBS_015</t>
+  </si>
+  <si>
+    <t>NSBS_016</t>
+  </si>
+  <si>
+    <t>NSBS_017</t>
+  </si>
+  <si>
+    <t>NSBS_018</t>
+  </si>
+  <si>
+    <t>NSBS_019</t>
+  </si>
+  <si>
+    <t>NSBS_020</t>
+  </si>
+  <si>
+    <t>NSBS_021</t>
+  </si>
+  <si>
+    <t>NSBS_022</t>
+  </si>
+  <si>
+    <t>NSBS_023</t>
+  </si>
+  <si>
+    <t>NSBS_024</t>
+  </si>
+  <si>
+    <t>NSBS_025</t>
+  </si>
+  <si>
+    <t>NSBS_026</t>
+  </si>
+  <si>
+    <t>NSBS_027</t>
+  </si>
+  <si>
+    <t>NSBS_028</t>
+  </si>
+  <si>
+    <t>NSBS_029</t>
+  </si>
+  <si>
+    <t>NSBS_030</t>
+  </si>
+  <si>
+    <t>NSBS_031</t>
+  </si>
+  <si>
+    <t>NWES_001</t>
+  </si>
+  <si>
+    <t>NWES_002</t>
+  </si>
+  <si>
+    <t>NWES_003</t>
+  </si>
+  <si>
+    <t>NWES_004</t>
+  </si>
+  <si>
+    <t>NWES_005</t>
+  </si>
+  <si>
+    <t>NWES_006</t>
+  </si>
+  <si>
+    <t>NWES_007</t>
+  </si>
+  <si>
+    <t>NWES_008</t>
+  </si>
+  <si>
+    <t>NWES_009</t>
+  </si>
+  <si>
+    <t>NWES_010</t>
+  </si>
+  <si>
+    <t>NWES_011</t>
+  </si>
+  <si>
+    <t>NWES_012</t>
+  </si>
+  <si>
+    <t>NWES_013</t>
+  </si>
+  <si>
+    <t>NWES_014</t>
+  </si>
+  <si>
+    <t>NWES_015</t>
+  </si>
+  <si>
+    <t>NWES_016</t>
+  </si>
+  <si>
+    <t>NWES_017</t>
+  </si>
+  <si>
+    <t>BALT_001</t>
+  </si>
+  <si>
+    <t>BALT_002</t>
+  </si>
+  <si>
+    <t>BALT_003</t>
+  </si>
+  <si>
+    <t>BALT_004</t>
+  </si>
+  <si>
+    <t>BALT_005</t>
+  </si>
+  <si>
+    <t>BALT_006</t>
+  </si>
+  <si>
+    <t>BALT_007</t>
+  </si>
+  <si>
+    <t>BALT_008</t>
+  </si>
+  <si>
+    <t>Station Description</t>
+  </si>
+  <si>
+    <t>Cape Desolation Section - Station 3 - Greenland Shelf</t>
+  </si>
+  <si>
+    <t>Fylla Section - Station 4 - Greenland Shelf</t>
+  </si>
+  <si>
+    <t>Nuuk Air Temperature</t>
+  </si>
+  <si>
+    <t>Fyllas Banke - Station 4 - Greenland Shelf</t>
+  </si>
+  <si>
+    <t>Gulf Of St Lawrence</t>
+  </si>
+  <si>
+    <t>Cartwright Air Temperature</t>
+  </si>
+  <si>
+    <t>CIL Layer Newfoundland and Labrador</t>
+  </si>
+  <si>
+    <t>Sea Ice Volume Newfoundland and Labrador</t>
+  </si>
+  <si>
+    <t>Station 27 - Newfoundland Shelf Temperature - Canada</t>
+  </si>
+  <si>
+    <t>Cabot Strait -  - Canada</t>
+  </si>
+  <si>
+    <t>Cabot Strait Sea Ice</t>
+  </si>
+  <si>
+    <t>Emerald Basin - Central Scotian Shelf - Canada</t>
+  </si>
+  <si>
+    <t>Georges Basin -  - Canada</t>
+  </si>
+  <si>
+    <t>Misaine Bank - North East Scotian Shelf - Canada</t>
+  </si>
+  <si>
+    <t>Sable Island Air Temperature</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Eastern Gulf of Maine</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Northeast Channel</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Northern Middle Atlantic Bight</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Northwest Georges Bank</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Southern Middle Atlantic Bight</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Western Gulf of Maine</t>
+  </si>
+  <si>
+    <t>Labrador Shelf - Canada</t>
+  </si>
+  <si>
+    <t>Newfoundland Shelf - Canada</t>
+  </si>
+  <si>
+    <t>Scotian Shelf - Canada</t>
+  </si>
+  <si>
+    <t>Gulf of Maine - Canada</t>
+  </si>
+  <si>
+    <t>Central Irminger Sea</t>
+  </si>
+  <si>
+    <t>East Greenland Slope Denmark Strait Overflow Water</t>
+  </si>
+  <si>
+    <t>Extended Ellett Line - Hatton Rockall Basin</t>
+  </si>
+  <si>
+    <t>Extended Ellett Line - Iceland Basin</t>
+  </si>
+  <si>
+    <t>Area2b HadISST 1.1 SST</t>
+  </si>
+  <si>
+    <t>Extended Ellett Line - Rockall Trough</t>
+  </si>
+  <si>
+    <t>Subpolar North Atlantic - Central Labrador Sea</t>
+  </si>
+  <si>
+    <t>Subpolar North Atlantic - Central Irminger Sea</t>
+  </si>
+  <si>
+    <t>Subpolar North Atlantic - Northern Iceland Basin</t>
+  </si>
+  <si>
+    <t>Subpolar North Atlantic - Central Iceland Basin</t>
+  </si>
+  <si>
+    <t>Subpolar North Atlantic - Rockall Trough</t>
+  </si>
+  <si>
+    <t>Santander Station 6 (Shelf Break) - Bay of Biscay - Spain</t>
+  </si>
+  <si>
+    <t>Santander Station 7 (Outer Slope) - Bay of Biscay - Spain</t>
+  </si>
+  <si>
+    <t>SP6 STOCA - Gulf of Cadiz Time Series</t>
+  </si>
+  <si>
+    <t>Raprocan Section - Canary Basin Coastal Transition Zone (stations 6-10)</t>
+  </si>
+  <si>
+    <t>Raprocan Section - Canary Basin Oceanic Waters (stations 11-24)</t>
+  </si>
+  <si>
+    <t>Finisterre Section - Western Iberian Margin</t>
+  </si>
+  <si>
+    <t>San Sebastian Sea Surface Temperature - Spain</t>
+  </si>
+  <si>
+    <t>Fugloya - Bear Island Section - Western Barents Sea - Atlantic Inflow</t>
+  </si>
+  <si>
+    <t>Kola Section - Eastern Barents Sea</t>
+  </si>
+  <si>
+    <t>VardÃ¸-North Section - Western Barents Sea - Atlantic Inflow</t>
+  </si>
+  <si>
+    <t>Faroe Coastal Skopun</t>
+  </si>
+  <si>
+    <t>Faroe Coastal Oyrargjogv</t>
+  </si>
+  <si>
+    <t>Faroe Bank Channel - West Faroe Islands</t>
+  </si>
+  <si>
+    <t>Faroe Current - North Faroe Islands (Modified North Atlantic Water)</t>
+  </si>
+  <si>
+    <t>Faroe Shetland Channel</t>
+  </si>
+  <si>
+    <t>Faroe Shetland Channel - Faroe Shelf (Modified North Atlantic Water)</t>
+  </si>
+  <si>
+    <t>Faroe Shetland Channel - Shetland Shelf (North Atlantic Water)</t>
+  </si>
+  <si>
+    <t>Fram Strait - East Greenland Current</t>
+  </si>
+  <si>
+    <t>Fram Strait - Return Atlantic Water</t>
+  </si>
+  <si>
+    <t>Fram Strait - West Spitsbergen Current</t>
+  </si>
+  <si>
+    <t>Central Norwegian Sea -  Gimsoy Section - Atlantic Water</t>
+  </si>
+  <si>
+    <t>Norwegian Sea -  Atlantic Water</t>
+  </si>
+  <si>
+    <t>Ocean Weather Station Mike</t>
+  </si>
+  <si>
+    <t>Northern Norwegian Sea - Sorkapp Section - Atlantic Water</t>
+  </si>
+  <si>
+    <t>Southern Norwegian Sea -  Svinoy Section - Atlantic Water</t>
+  </si>
+  <si>
+    <t>Greenland Sea section - West of Spitsbergen 76.5N</t>
+  </si>
+  <si>
+    <t>Akureyri Air Temperature</t>
+  </si>
+  <si>
+    <t>Iceland Deep Data 1800m</t>
+  </si>
+  <si>
+    <t>Reykavik Air Temperature</t>
+  </si>
+  <si>
+    <t>Selvogsbanki Station 5 - South West Iceland - Irminger Current - Spring</t>
+  </si>
+  <si>
+    <t>Siglunes Station 2-4 - North Iceland - North Icelandic Irminger Current - Spring</t>
+  </si>
+  <si>
+    <t>Faxafloi Station 9 - Northern Irminger Sea - Winter</t>
+  </si>
+  <si>
+    <t>Faroe Section N - Station N14 (Deep water)</t>
+  </si>
+  <si>
+    <t>Faroe Section N - Stations N05-N10 (Intermediate water)</t>
+  </si>
+  <si>
+    <t>Faroe Shetland Channel</t>
+  </si>
+  <si>
+    <t>Langanes Station 2-6 - North East Iceland - East Icelandic Current - Spring</t>
+  </si>
+  <si>
+    <t>Eastern Greenland Sea - Atlantic Water</t>
+  </si>
+  <si>
+    <t>Point 33 - Astan</t>
+  </si>
+  <si>
+    <t>M3 Marine Weather Buoy</t>
+  </si>
+  <si>
+    <t>Malin Head Weather Station</t>
+  </si>
+  <si>
+    <t>38a Oceanographic Mooring</t>
+  </si>
+  <si>
+    <t>North Sea - Helgoland Roads</t>
+  </si>
+  <si>
+    <t>North Sea SST</t>
+  </si>
+  <si>
+    <t>Fair Isle Current Water (Waters entering North Sea from Atlantic)</t>
+  </si>
+  <si>
+    <t>Felixstowe-Gabbard - 52N - Ferry merged Smartbuoy</t>
+  </si>
+  <si>
+    <t>Modelled North Sea Inflow</t>
+  </si>
+  <si>
+    <t>North Sea Utsira A</t>
+  </si>
+  <si>
+    <t>North Sea Utsira B</t>
+  </si>
+  <si>
+    <t>Western Channel Observatory (WCO) - E1 - UK</t>
+  </si>
+  <si>
+    <t>Central Skagerrak</t>
+  </si>
+  <si>
+    <t>Cooled Atlantic Water (Atlantic Water below the seasonal thermocline in central Northern North Sea)</t>
+  </si>
+  <si>
+    <t>Baltic Proper - East of Gotland - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Baltic - G2 - Gulf of Gdansk</t>
+  </si>
+  <si>
+    <t>Baltic Proper - SMHI Observed Ice Extent</t>
+  </si>
+  <si>
+    <t>Baltic - LL12 - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Baltic - LL15 - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Baltic - LL7 - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Baltic - SR5 - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Baltic - US5B - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>60.47 N</t>
+  </si>
+  <si>
+    <t>63.88 N</t>
+  </si>
+  <si>
+    <t>64.2 N</t>
+  </si>
+  <si>
+    <t>63.88 N</t>
+  </si>
+  <si>
+    <t>48.5 N</t>
+  </si>
+  <si>
+    <t>53.7 N</t>
+  </si>
+  <si>
+    <t>49.5 N</t>
+  </si>
+  <si>
+    <t>50 N</t>
+  </si>
+  <si>
+    <t>47.55 N</t>
+  </si>
+  <si>
+    <t>47.3N</t>
+  </si>
+  <si>
+    <t>46.5 N</t>
+  </si>
+  <si>
+    <t>44 N</t>
+  </si>
+  <si>
+    <t>42.5N</t>
+  </si>
+  <si>
+    <t>45 N</t>
+  </si>
+  <si>
+    <t>43.93 N</t>
+  </si>
+  <si>
+    <t>43 N</t>
+  </si>
+  <si>
+    <t>42.2 N</t>
+  </si>
+  <si>
+    <t>40 N</t>
+  </si>
+  <si>
+    <t>41.5 N</t>
+  </si>
+  <si>
+    <t>38.25 N</t>
+  </si>
+  <si>
+    <t>43 N</t>
+  </si>
+  <si>
+    <t>56.5 N</t>
+  </si>
+  <si>
+    <t>47 N</t>
+  </si>
+  <si>
+    <t>44 N</t>
+  </si>
+  <si>
+    <t>42.5 N</t>
+  </si>
+  <si>
+    <t>59.4 N</t>
+  </si>
+  <si>
+    <t>59.6 N</t>
+  </si>
+  <si>
+    <t>58.66 N</t>
+  </si>
+  <si>
+    <t>60.00 N</t>
+  </si>
+  <si>
+    <t>56.5 N</t>
+  </si>
+  <si>
+    <t>57.5 N</t>
+  </si>
+  <si>
+    <t>57.18 N</t>
+  </si>
+  <si>
+    <t>58.71 N</t>
+  </si>
+  <si>
+    <t>60.01 N</t>
+  </si>
+  <si>
+    <t>57.84 N</t>
+  </si>
+  <si>
+    <t>55.56 N</t>
+  </si>
+  <si>
+    <t>43.708 N</t>
+  </si>
+  <si>
+    <t>43.800 N</t>
+  </si>
+  <si>
+    <t>36.145 N</t>
+  </si>
+  <si>
+    <t>28.5 N</t>
+  </si>
+  <si>
+    <t>29 N</t>
+  </si>
+  <si>
+    <t>43 N</t>
+  </si>
+  <si>
+    <t>43.323 N</t>
+  </si>
+  <si>
+    <t>73 N</t>
+  </si>
+  <si>
+    <t>71.5 N</t>
+  </si>
+  <si>
+    <t>73 N</t>
+  </si>
+  <si>
+    <t>61.91 N</t>
+  </si>
+  <si>
+    <t>62.12 N</t>
+  </si>
+  <si>
+    <t>61.4 N</t>
+  </si>
+  <si>
+    <t>63 N</t>
+  </si>
+  <si>
+    <t>61.25 N</t>
+  </si>
+  <si>
+    <t>61.5 N</t>
+  </si>
+  <si>
+    <t>61 N</t>
+  </si>
+  <si>
+    <t>78.83 N</t>
+  </si>
+  <si>
+    <t>69 N</t>
+  </si>
+  <si>
+    <t>70 N</t>
+  </si>
+  <si>
+    <t>66 N</t>
+  </si>
+  <si>
+    <t>76.33 N</t>
+  </si>
+  <si>
+    <t>63 N</t>
+  </si>
+  <si>
+    <t>76.5 N</t>
+  </si>
+  <si>
+    <t>65.41 N</t>
+  </si>
+  <si>
+    <t>68 N</t>
+  </si>
+  <si>
+    <t>64.08 N</t>
+  </si>
+  <si>
+    <t>63.00 N</t>
+  </si>
+  <si>
+    <t>67 N</t>
+  </si>
+  <si>
+    <t>64.2 N</t>
+  </si>
+  <si>
+    <t>64.5 N</t>
+  </si>
+  <si>
+    <t>63.416 N</t>
+  </si>
+  <si>
+    <t>61.25 N</t>
+  </si>
+  <si>
+    <t>67.5 N</t>
+  </si>
+  <si>
+    <t>75 N</t>
+  </si>
+  <si>
+    <t>48.78 N</t>
+  </si>
+  <si>
+    <t>51.22 N</t>
+  </si>
+  <si>
+    <t>55.37 N</t>
+  </si>
+  <si>
+    <t>53.783 N</t>
+  </si>
+  <si>
+    <t>54.183 N</t>
+  </si>
+  <si>
+    <t>55.99 N</t>
+  </si>
+  <si>
+    <t>59 N</t>
+  </si>
+  <si>
+    <t>52 N</t>
+  </si>
+  <si>
+    <t>59 N</t>
+  </si>
+  <si>
+    <t>50.033 N</t>
+  </si>
+  <si>
+    <t>58.133 N</t>
+  </si>
+  <si>
+    <t>57.933 N</t>
+  </si>
+  <si>
+    <t>58.133 N</t>
+  </si>
+  <si>
+    <t>59 N</t>
+  </si>
+  <si>
+    <t>57.5 N</t>
+  </si>
+  <si>
+    <t>54.833 N</t>
+  </si>
+  <si>
+    <t>65 N</t>
+  </si>
+  <si>
+    <t>59.48 N</t>
+  </si>
+  <si>
+    <t>59.18 N</t>
+  </si>
+  <si>
+    <t>59.85 N</t>
+  </si>
+  <si>
+    <t>61.08 N</t>
+  </si>
+  <si>
+    <t>62.59 N</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>50.00 W</t>
+  </si>
+  <si>
+    <t>53.37 W</t>
+  </si>
+  <si>
+    <t>51.8 W</t>
+  </si>
+  <si>
+    <t>53.37 W</t>
+  </si>
+  <si>
+    <t>61.0 W</t>
+  </si>
+  <si>
+    <t>57.0 W</t>
+  </si>
+  <si>
+    <t>50.5 W</t>
+  </si>
+  <si>
+    <t>50 W</t>
+  </si>
+  <si>
+    <t>52.59 W</t>
+  </si>
+  <si>
+    <t>60.3W</t>
+  </si>
+  <si>
+    <t>58.5 W</t>
+  </si>
+  <si>
+    <t>63 W</t>
+  </si>
+  <si>
+    <t>67W</t>
+  </si>
+  <si>
+    <t>59 W</t>
+  </si>
+  <si>
+    <t>59.97 W</t>
+  </si>
+  <si>
+    <t>67 W</t>
+  </si>
+  <si>
+    <t>66 W</t>
+  </si>
+  <si>
+    <t>71 W</t>
+  </si>
+  <si>
+    <t>68.3 W</t>
+  </si>
+  <si>
+    <t>74.5 W</t>
+  </si>
+  <si>
+    <t>69 W</t>
+  </si>
+  <si>
+    <t>59 W</t>
+  </si>
+  <si>
+    <t>50 W</t>
+  </si>
+  <si>
+    <t>61.5 W</t>
+  </si>
+  <si>
+    <t>69 W</t>
+  </si>
+  <si>
+    <t>36.8 W</t>
+  </si>
+  <si>
+    <t>38.8 W</t>
+  </si>
+  <si>
+    <t>16.50 W</t>
+  </si>
+  <si>
+    <t>20.00 W</t>
+  </si>
+  <si>
+    <t>52.5 W</t>
+  </si>
+  <si>
+    <t>11.00 W</t>
+  </si>
+  <si>
+    <t>51.95 W</t>
+  </si>
+  <si>
+    <t>39.23 W</t>
+  </si>
+  <si>
+    <t>19.67 W</t>
+  </si>
+  <si>
+    <t>25.76 W</t>
+  </si>
+  <si>
+    <t>12.91 W</t>
+  </si>
+  <si>
+    <t>3.786 W</t>
+  </si>
+  <si>
+    <t>3.784 W</t>
+  </si>
+  <si>
+    <t>6.713 W</t>
+  </si>
+  <si>
+    <t>13 W</t>
+  </si>
+  <si>
+    <t>16 W</t>
+  </si>
+  <si>
+    <t>12.15 W</t>
+  </si>
+  <si>
+    <t>1.9922 W</t>
+  </si>
+  <si>
+    <t>20 E</t>
+  </si>
+  <si>
+    <t>33.5 E</t>
+  </si>
+  <si>
+    <t>31.2 E</t>
+  </si>
+  <si>
+    <t>6.88 W</t>
+  </si>
+  <si>
+    <t>7.17 W</t>
+  </si>
+  <si>
+    <t>8.3 W</t>
+  </si>
+  <si>
+    <t>6 W</t>
+  </si>
+  <si>
+    <t>4.5 W</t>
+  </si>
+  <si>
+    <t>6 W</t>
+  </si>
+  <si>
+    <t>3 W</t>
+  </si>
+  <si>
+    <t>6 W</t>
+  </si>
+  <si>
+    <t>1 E</t>
+  </si>
+  <si>
+    <t>7 E</t>
+  </si>
+  <si>
+    <t>12 E</t>
+  </si>
+  <si>
+    <t>0 E</t>
+  </si>
+  <si>
+    <t>2 E</t>
+  </si>
+  <si>
+    <t>10 E</t>
+  </si>
+  <si>
+    <t>3 E</t>
+  </si>
+  <si>
+    <t>10.5 E</t>
+  </si>
+  <si>
+    <t>18.05 W</t>
+  </si>
+  <si>
+    <t>12 W</t>
+  </si>
+  <si>
+    <t>21.54 W</t>
+  </si>
+  <si>
+    <t>21.47 W</t>
+  </si>
+  <si>
+    <t>18 W</t>
+  </si>
+  <si>
+    <t>28 W</t>
+  </si>
+  <si>
+    <t>6 W</t>
+  </si>
+  <si>
+    <t>6.083 W</t>
+  </si>
+  <si>
+    <t>4.5 W</t>
+  </si>
+  <si>
+    <t>13.5 W</t>
+  </si>
+  <si>
+    <t>11.5 E</t>
+  </si>
+  <si>
+    <t>3.94 W</t>
+  </si>
+  <si>
+    <t>10.55 W</t>
+  </si>
+  <si>
+    <t>7.34 W</t>
+  </si>
+  <si>
+    <t>5.625 W</t>
+  </si>
+  <si>
+    <t>7.9 E</t>
+  </si>
+  <si>
+    <t>3.201 E</t>
+  </si>
+  <si>
+    <t>2 W</t>
+  </si>
+  <si>
+    <t>2 E</t>
+  </si>
+  <si>
+    <t>1 E</t>
+  </si>
+  <si>
+    <t>0.5 E</t>
+  </si>
+  <si>
+    <t>4 E</t>
+  </si>
+  <si>
+    <t>4.367 W</t>
+  </si>
+  <si>
+    <t>9.183 E</t>
+  </si>
+  <si>
+    <t>9.450 E</t>
+  </si>
+  <si>
+    <t>9.183 E</t>
+  </si>
+  <si>
+    <t>0.5 W</t>
+  </si>
+  <si>
+    <t>19.5 E</t>
+  </si>
+  <si>
+    <t>19.316 E</t>
+  </si>
+  <si>
+    <t>23 E</t>
+  </si>
+  <si>
+    <t>22.90 E</t>
+  </si>
+  <si>
+    <t>21.75 E</t>
+  </si>
+  <si>
+    <t>24.84 E</t>
+  </si>
+  <si>
+    <t>19.58 E</t>
+  </si>
+  <si>
+    <t>19.97 E</t>
+  </si>
+  <si>
+    <t>Measurement Depth (m)</t>
+  </si>
+  <si>
+    <t>75-200 m</t>
+  </si>
+  <si>
+    <t>2000 m</t>
+  </si>
+  <si>
+    <t>0-50 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>0-50 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Land Surface</t>
+  </si>
+  <si>
+    <t>0-176 m</t>
+  </si>
+  <si>
+    <t>200 - 300 m (Near Bottom)</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>250 m (Near Bottom)</t>
+  </si>
+  <si>
+    <t>200 m (Near Bottom)</t>
+  </si>
+  <si>
+    <t>100 m (Near Bottom)</t>
+  </si>
+  <si>
+    <t>1-30 m</t>
+  </si>
+  <si>
+    <t>150-200 m</t>
+  </si>
+  <si>
+    <t>1-30 m</t>
+  </si>
+  <si>
+    <t>1-30m</t>
+  </si>
+  <si>
+    <t>1-30 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>1600-2000 m</t>
+  </si>
+  <si>
+    <t>200-400 m</t>
+  </si>
+  <si>
+    <t>Near Bottom</t>
+  </si>
+  <si>
+    <t>Upper 800 m</t>
+  </si>
+  <si>
+    <t>Deep Ocean 2000-2700m</t>
+  </si>
+  <si>
+    <t>Intermediate Ocean 1000-2000m</t>
+  </si>
+  <si>
+    <t>Upper Ocean 30-600m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Intermediate Ocean 1500-2300m</t>
+  </si>
+  <si>
+    <t>Upper Ocean 30-800m</t>
+  </si>
+  <si>
+    <t>15-200 m</t>
+  </si>
+  <si>
+    <t>200-1500 m</t>
+  </si>
+  <si>
+    <t>15-200 m</t>
+  </si>
+  <si>
+    <t>200-1500 m</t>
+  </si>
+  <si>
+    <t>15-200 m</t>
+  </si>
+  <si>
+    <t>200-1500 m</t>
+  </si>
+  <si>
+    <t>15-200 m</t>
+  </si>
+  <si>
+    <t>200-1500 m</t>
+  </si>
+  <si>
+    <t>15-200 m</t>
+  </si>
+  <si>
+    <t>200-1500 m</t>
+  </si>
+  <si>
+    <t>0-30 m</t>
+  </si>
+  <si>
+    <t>300-600 m</t>
+  </si>
+  <si>
+    <t>600-950 m</t>
+  </si>
+  <si>
+    <t>0-20 m</t>
+  </si>
+  <si>
+    <t>1-20 m</t>
+  </si>
+  <si>
+    <t>100-300 m</t>
+  </si>
+  <si>
+    <t>300-600 m</t>
+  </si>
+  <si>
+    <t>25-150 dbar</t>
+  </si>
+  <si>
+    <t>200-800 dbar</t>
+  </si>
+  <si>
+    <t>800-1200 dbar</t>
+  </si>
+  <si>
+    <t>200-800 dbar</t>
+  </si>
+  <si>
+    <t>800-1400 dbar</t>
+  </si>
+  <si>
+    <t>1400-2600 dbar</t>
+  </si>
+  <si>
+    <t>2600-3600 dbar</t>
+  </si>
+  <si>
+    <t>200-800m</t>
+  </si>
+  <si>
+    <t>800-2000m</t>
+  </si>
+  <si>
+    <t>2000-5500m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>50-200 m</t>
+  </si>
+  <si>
+    <t>0-200 m</t>
+  </si>
+  <si>
+    <t>50-200 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Upper Layer High Salinity Core</t>
+  </si>
+  <si>
+    <t>800 m</t>
+  </si>
+  <si>
+    <t>Upper Layer - typically between  0-200m</t>
+  </si>
+  <si>
+    <t>50-500 m</t>
+  </si>
+  <si>
+    <t>50-200 m</t>
+  </si>
+  <si>
+    <t>0-800 m</t>
+  </si>
+  <si>
+    <t>2000 m</t>
+  </si>
+  <si>
+    <t>50 m</t>
+  </si>
+  <si>
+    <t>50-200 m</t>
+  </si>
+  <si>
+    <t>200 m</t>
+  </si>
+  <si>
+    <t>1500-1800 m</t>
+  </si>
+  <si>
+    <t>0-200 m</t>
+  </si>
+  <si>
+    <t>50-150 m</t>
+  </si>
+  <si>
+    <t>200-500 m</t>
+  </si>
+  <si>
+    <t>1800-2000 m</t>
+  </si>
+  <si>
+    <t>800-1000 m</t>
+  </si>
+  <si>
+    <t>1000 m</t>
+  </si>
+  <si>
+    <t>1100 m</t>
+  </si>
+  <si>
+    <t>0-50 m</t>
+  </si>
+  <si>
+    <t>50-150 m</t>
+  </si>
+  <si>
+    <t>2 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Seabed</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>0-100 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Depth Averaged</t>
+  </si>
+  <si>
+    <t>Nearbed</t>
+  </si>
+  <si>
+    <t>0-40 m</t>
+  </si>
+  <si>
+    <t>Surface-water</t>
+  </si>
+  <si>
+    <t>Deep-water</t>
+  </si>
+  <si>
+    <t>Bottom-water</t>
+  </si>
+  <si>
+    <t>50-100 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>75 m</t>
+  </si>
+  <si>
+    <t>120 m</t>
+  </si>
+  <si>
+    <t>70 m</t>
+  </si>
+  <si>
+    <t>110 m</t>
+  </si>
+  <si>
+    <t>200 m</t>
+  </si>
+  <si>
+    <t>Data Source</t>
+  </si>
+  <si>
+    <t>Thünen-Institut für Seefischerei - Germany - Thünen Institute of Sea Fisheries</t>
+  </si>
+  <si>
+    <t>Danish Meteorological Institute - Copenhagen</t>
+  </si>
+  <si>
+    <t>Greenland Institute of Natural Resources</t>
+  </si>
+  <si>
+    <t>Department of Fisheries and Oceans - Canada</t>
+  </si>
+  <si>
+    <t>Northwest Atlantic Fisheries Centre - Canada</t>
+  </si>
+  <si>
+    <t>Department of Fisheries and Oceans - Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department of Fisheries and Oceans - Canada </t>
+  </si>
+  <si>
+    <t>Department of Fisheries and Oceans - Canada</t>
+  </si>
+  <si>
+    <t>NOAA Fisheries - NEFSC - Oceans and Climate Branch - USA</t>
+  </si>
+  <si>
+    <t>Department of Fisheries and Oceans - Canada</t>
+  </si>
+  <si>
+    <t>Koninklijk Nederlands Instituut voor Zeeonderzoek (NIOZ) - Royal Netherlands Institute for Sea Research</t>
+  </si>
+  <si>
+    <t>National Oceanography Centre and Scottish Association for Marine Science - UK</t>
+  </si>
+  <si>
+    <t>Met Office Hadley Centre - UK</t>
+  </si>
+  <si>
+    <t>National Oceanography Centre and Scottish Association for Marine Science - UK</t>
+  </si>
+  <si>
+    <t>"The Deep-Ocean Observation and Research Synthesis (DOORS). Oceanographic observations included in the DOORS are obtained from multiple sources</t>
+  </si>
+  <si>
+    <t>IEO-CSIC Spanish Institute of Oceanography www.ieo.es - Spain</t>
+  </si>
+  <si>
+    <t>IEO-CSIC - Instituto Espanol de Oceanografia - Spanish Institute of Oceanography - Spain</t>
+  </si>
+  <si>
+    <t>IEO-CSIC Instituto Espanol de Oceanografia - Spanish Institute of Oceanography - Spain</t>
+  </si>
+  <si>
+    <t>IEO - Instituto Espanol de Oceanografia - Spanish Institute of Oceanography - Spain</t>
+  </si>
+  <si>
+    <t>IEO-CSIC - Instituto Espanol de Oceanografia - Spanish Institute of Oceanography - Spain</t>
+  </si>
+  <si>
+    <t>Aquarium of San Sebastian (Oceanographic Society of Gipuzkoa and Oceanographic Foundation of Gipuzkoa) - Spain</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>PINRO - Polar Branch of the Russian Federal Research Institute of Fisheries and Oceanography - Russia</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>Havstovan - Faroe - Faroe Marine Research Institute</t>
+  </si>
+  <si>
+    <t>SGMD - Scottish Government Marine Directorate - Aberdeen - UK</t>
+  </si>
+  <si>
+    <t>AWI - Alfred Wegener Institute for Polar and Marine Research - Germany and NPI - Norwegian Polar Institute - Norway</t>
+  </si>
+  <si>
+    <t>AWI - Alfred Wegener Institute for Polar and Marine Research - Germany and IOPAN - Institute of Oceanology Polish Academy of Sciences - Poland</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>Institut of Marine Research Bergen - Norway</t>
+  </si>
+  <si>
+    <t>Geophysical Institute - University of Bergen - Norway</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>IOPAS - Institute of Oceanology Polish Academy of Sciences - Poland</t>
+  </si>
+  <si>
+    <t>Hafrannsoknastofnun - Iceland - IcelandicMetoffice via Marine Research Institute</t>
+  </si>
+  <si>
+    <t>Hafrannsoknastofnun - Iceland - Marine Research Institute</t>
+  </si>
+  <si>
+    <t>Hafrannsoknastofnun - Iceland - Icelandic Metoffice via Marine Research Institute</t>
+  </si>
+  <si>
+    <t>Hafrannsoknastofnun - Iceland - Marine Research Institute</t>
+  </si>
+  <si>
+    <t>Havstovan - Faroe - Faroe Marine Research Institute</t>
+  </si>
+  <si>
+    <t>SGMD - Scottish Government Marine Directorate - Aberdeen - UK</t>
+  </si>
+  <si>
+    <t>Hafrannsoknastofnun - Iceland - Marine Research Institute</t>
+  </si>
+  <si>
+    <t>AWI - Alfred Wegener Institute for Polar and Marine Research - Germany and IOPAN - Institute of Oceanology Polish Academy of Sciences - Poland</t>
+  </si>
+  <si>
+    <t>CNRS - Observatoire Oceanologique de Roscoff - France</t>
+  </si>
+  <si>
+    <t>Marine Institute Ireland</t>
+  </si>
+  <si>
+    <t>Marine Institute/Met Eireann - Ireland</t>
+  </si>
+  <si>
+    <t>AFBI Northern Ireland</t>
+  </si>
+  <si>
+    <t>Alfred-Wegener-Institut (AWI) - Helmholtz-Zentrum für Polar- und Meeresforschung</t>
+  </si>
+  <si>
+    <t>BSH - German Federal Maritime and Hydrographic Agency</t>
+  </si>
+  <si>
+    <t>SGMD - Scottish Government Marine Directorate - Aberdeen - UK</t>
+  </si>
+  <si>
+    <t>CEFAS - Centre for Environment Fisheries and Aquaculture Science - UK</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>Marine Biological Association and Plymouth Marine Laboratory - UK</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>SGMD - Scottish Government Marine Directorate - Aberdeen - UK</t>
+  </si>
+  <si>
+    <t>SMHI - Swedish Meteorological and Hydrological Institute</t>
+  </si>
+  <si>
+    <t>National Marine Fisheries Research Institute - Poland (MIR-PIB)</t>
+  </si>
+  <si>
+    <t>SMHI - Swedish Meteorological and Hydrological Institute</t>
+  </si>
+  <si>
+    <t>FMI - Finnish Meteorological Institute - Finland</t>
+  </si>
+  <si>
+    <t>Contact Name</t>
+  </si>
+  <si>
+    <t>Boris Cisewski (boris.cisewski@thuenen.de)</t>
+  </si>
+  <si>
+    <t>John Mortensen (jomo@natur.gl)</t>
+  </si>
+  <si>
+    <t>Peter Galbraith (Peter.Galbraith@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Jonathan Coyne (Jonathan.Coyne@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Jonathna Coyne (Jonathan.Coyne@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Jonathan Coyne (Jonathan.Coyne@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Chantelle Layton (Chantelle.Layton@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>David Hebert (David.Hebert@dfo-mpo.gc.ca);Chantelle Layton (Chantelle.Layton@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Chantelle Layton (Chantelle.Layton@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Paula Fratantoni (paula.fratantoni@noaa.gov)</t>
+  </si>
+  <si>
+    <t>Peter Galbraith (Peter.Galbraith@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Femke de Jong (femke.de.jong@nioz.nl)</t>
+  </si>
+  <si>
+    <t>Sam Jones (sam.jones@sams.ac.uk)</t>
+  </si>
+  <si>
+    <t>Bee Berx &amp; Berit Rabe (MD.Oceanography@gov.scot)</t>
+  </si>
+  <si>
+    <t>Sam Jones (sam.jones@sams.ac.uk)</t>
+  </si>
+  <si>
+    <t>"Igor Yashayaev (Igor.Yashayaev@dfo-mpo.gc.ca)"</t>
+  </si>
+  <si>
+    <t>Cesar Gonzalez-Pola (cesar.pola@ieo.csic.es)</t>
+  </si>
+  <si>
+    <t>Ricardo F. Sanchez Leal (rleal@ieo.csic.es)</t>
+  </si>
+  <si>
+    <t>Angela Mosquera Gimenez (angela.mosquera@ieo.csic.es);Pedro Velez Belchi (pedro.velez@ieo.csic.es)</t>
+  </si>
+  <si>
+    <t>Angela Mosquera Gimenez (angela.mosquera@ieo.csic.es);Pedro Velez Belchi (pedro.velez@ieo.es)</t>
+  </si>
+  <si>
+    <t>Angela Mosquera Gimenez (angela.mosquera@ieo.csic.es);Pedro Velez Belchi (pedro.velez@ieo.csic.es)</t>
+  </si>
+  <si>
+    <t>Angela Mosquera Gimenez (angela.mosquera@ieo.csic.es);Pedro Velez Belchi (pedro.velez@ieo.es)</t>
+  </si>
+  <si>
+    <t>Cesar Gonzalez-Pola (cesar.pola@ieo.csic.es)</t>
+  </si>
+  <si>
+    <t>Almudena Fontan (afontan@azti.es)</t>
+  </si>
+  <si>
+    <t>Randi Ingvaldsen (randi.ingvaldsen@imr.no)</t>
+  </si>
+  <si>
+    <t>Alexander G. Trofimov (trofimov@pinro.ru)</t>
+  </si>
+  <si>
+    <t>Randi Ingvaldsen (randi.ingvaldsen@imr.no)</t>
+  </si>
+  <si>
+    <t>Karin Margretha H. Larsen (KarinL@hav.fo)</t>
+  </si>
+  <si>
+    <t>Bee Berx &amp; Berit Rabe (MD.Oceanography@gov.scot)</t>
+  </si>
+  <si>
+    <t>Wilken Jon von Appen (wjvappen@awi.de) and Paul Dodd (Paul.Dodd@npi.no)</t>
+  </si>
+  <si>
+    <t>Wilken Jon von Appen (wjvappen@awi.de) and Agnieszka Beszczynska-M_ller (abesz@iopan.gda.pl)</t>
+  </si>
+  <si>
+    <t>Kjell Arne Mork (kjell.arne.mork@imr.no)</t>
+  </si>
+  <si>
+    <t>Svein Ã˜sterhus (Svein.Osterhus@norceresearch.no)</t>
+  </si>
+  <si>
+    <t>Svein Osterhus (Svein.Osterhus@gfi.uib.no)</t>
+  </si>
+  <si>
+    <t>Kjell Arne Mork (kjell.arne.mork@imr.no)</t>
+  </si>
+  <si>
+    <t>Waldemar Walczowski (walczows@iopan.gda.pl)</t>
+  </si>
+  <si>
+    <t>Solveig R. Olafsdottir (solveig.rosa.olafsdottir@hafogvatn.is)</t>
+  </si>
+  <si>
+    <t>Karin Margretha H. Larsen (KarinL@hav.fo)</t>
+  </si>
+  <si>
+    <t>Bee Berx &amp; Berit Rabe (MD.Oceanography@gov.scot)</t>
+  </si>
+  <si>
+    <t>Solveig R. Olafsdottir (solveig.rosa.olafsdottir@hafogvatn.is)</t>
+  </si>
+  <si>
+    <t>Wilken Jon von Appen (wjvappen@awi.de) and Agnieszka Beszczynska-MÃ¶ller (abesz@iopan.pl)</t>
+  </si>
+  <si>
+    <t>Pascal Morin (pmorin@sb-roscoff.fr)</t>
+  </si>
+  <si>
+    <t>Eoghan Daly (eoghan.daly@marine.ie)</t>
+  </si>
+  <si>
+    <t>Billy Hunter (billy.hunter@afbini.gov.uk)</t>
+  </si>
+  <si>
+    <t>Inga Kirstein (inga.kirstein@awi.de)</t>
+  </si>
+  <si>
+    <t>Dagmar Kieke (dagmar.kieke@bsh.de)</t>
+  </si>
+  <si>
+    <t>Bee Berx &amp; Berit Rabe (MD.Oceanography@gov.scot)</t>
+  </si>
+  <si>
+    <t>Lianne Harrison (lianne.harrison@cefas.gov.uk)</t>
+  </si>
+  <si>
+    <t>Jon Albretsen (jon.albretsen@hi.no)</t>
+  </si>
+  <si>
+    <t>Tim J. Smyth (tjsm@pml.ac.uk)</t>
+  </si>
+  <si>
+    <t>Jon Albretsen (jon.albretsen@hi.no)</t>
+  </si>
+  <si>
+    <t>Bee Berx &amp; Berit Rabe (MD.Oceanography@gov.scot)</t>
+  </si>
+  <si>
+    <t>Johanna Linders (johanna.linders@smhi.se)</t>
+  </si>
+  <si>
+    <t>Tycjan Wodzinowski (twodzinowski@mir.gdynia.pl)</t>
+  </si>
+  <si>
+    <t>Johanna Linders (johanna.linders@smhi.se)</t>
+  </si>
+  <si>
+    <t>Antti Westerlund (antti.westerlund@fmi.fi)</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>BBAY</t>
+  </si>
+  <si>
+    <t>NEAS</t>
+  </si>
+  <si>
+    <t>SPNA</t>
+  </si>
+  <si>
+    <t>BICC</t>
+  </si>
+  <si>
+    <t>NSBS</t>
+  </si>
+  <si>
+    <t>NWES</t>
+  </si>
+  <si>
+    <t>BALT</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>BBAY_001</t>
+  </si>
+  <si>
+    <t>BBAY_002</t>
+  </si>
+  <si>
+    <t>BBAY_003</t>
+  </si>
+  <si>
+    <t>BBAY_004</t>
+  </si>
+  <si>
+    <t>BBAY_005</t>
+  </si>
+  <si>
+    <t>NEAS_001</t>
+  </si>
+  <si>
+    <t>NEAS_002</t>
+  </si>
+  <si>
+    <t>NEAS_003</t>
+  </si>
+  <si>
+    <t>NEAS_004</t>
+  </si>
+  <si>
+    <t>NEAS_005</t>
+  </si>
+  <si>
+    <t>NEAS_006</t>
+  </si>
+  <si>
+    <t>NEAS_007</t>
+  </si>
+  <si>
+    <t>NEAS_008</t>
+  </si>
+  <si>
+    <t>NEAS_009</t>
+  </si>
+  <si>
+    <t>NEAS_010</t>
+  </si>
+  <si>
+    <t>NEAS_011</t>
+  </si>
+  <si>
+    <t>NEAS_012</t>
+  </si>
+  <si>
+    <t>NEAS_013</t>
+  </si>
+  <si>
+    <t>NEAS_014</t>
+  </si>
+  <si>
+    <t>NEAS_015</t>
+  </si>
+  <si>
+    <t>NEAS_016</t>
+  </si>
+  <si>
+    <t>NEAS_017</t>
+  </si>
+  <si>
+    <t>NEAS_018</t>
+  </si>
+  <si>
+    <t>NEAS_019</t>
+  </si>
+  <si>
+    <t>NEAS_020</t>
+  </si>
+  <si>
+    <t>NEAS_021</t>
+  </si>
+  <si>
+    <t>SPNA_001</t>
+  </si>
+  <si>
+    <t>SPNA_002</t>
+  </si>
+  <si>
+    <t>SPNA_003</t>
+  </si>
+  <si>
+    <t>SPNA_004</t>
+  </si>
+  <si>
+    <t>SPNA_006</t>
+  </si>
+  <si>
+    <t>SPNA_007</t>
+  </si>
+  <si>
+    <t>SPNA_008</t>
+  </si>
+  <si>
+    <t>SPNA_017</t>
+  </si>
+  <si>
+    <t>SPNA_018</t>
+  </si>
+  <si>
+    <t>SPNA_019</t>
+  </si>
+  <si>
+    <t>SPNA_020</t>
+  </si>
+  <si>
+    <t>SPNA_021</t>
+  </si>
+  <si>
+    <t>SPNA_022</t>
+  </si>
+  <si>
+    <t>SPNA_023</t>
+  </si>
+  <si>
+    <t>SPNA_024</t>
+  </si>
+  <si>
+    <t>SPNA_025</t>
+  </si>
+  <si>
+    <t>SPNA_026</t>
+  </si>
+  <si>
+    <t>SPNA_027</t>
+  </si>
+  <si>
+    <t>SPNA_028</t>
+  </si>
+  <si>
+    <t>SPNA_029</t>
+  </si>
+  <si>
+    <t>BICC_003</t>
+  </si>
+  <si>
+    <t>BICC_004</t>
+  </si>
+  <si>
+    <t>BICC_005</t>
+  </si>
+  <si>
+    <t>BICC_006</t>
+  </si>
+  <si>
+    <t>BICC_007</t>
+  </si>
+  <si>
+    <t>BICC_008</t>
+  </si>
+  <si>
+    <t>BICC_009</t>
+  </si>
+  <si>
+    <t>BICC_010</t>
+  </si>
+  <si>
+    <t>BICC_011</t>
+  </si>
+  <si>
+    <t>BICC_012</t>
+  </si>
+  <si>
+    <t>BICC_013</t>
+  </si>
+  <si>
+    <t>BICC_014</t>
+  </si>
+  <si>
+    <t>BICC_015</t>
+  </si>
+  <si>
+    <t>BICC_016</t>
+  </si>
+  <si>
+    <t>BICC_017</t>
+  </si>
+  <si>
+    <t>BICC_018</t>
+  </si>
+  <si>
+    <t>BICC_110</t>
+  </si>
+  <si>
+    <t>NSBS_001</t>
+  </si>
+  <si>
+    <t>NSBS_002</t>
+  </si>
+  <si>
+    <t>NSBS_003</t>
+  </si>
+  <si>
+    <t>NSBS_004</t>
+  </si>
+  <si>
+    <t>NSBS_005</t>
+  </si>
+  <si>
+    <t>NSBS_006</t>
+  </si>
+  <si>
+    <t>NSBS_007</t>
+  </si>
+  <si>
+    <t>NSBS_008</t>
+  </si>
+  <si>
+    <t>NSBS_009</t>
+  </si>
+  <si>
+    <t>NSBS_010</t>
+  </si>
+  <si>
+    <t>NSBS_011</t>
+  </si>
+  <si>
+    <t>NSBS_012</t>
+  </si>
+  <si>
+    <t>NSBS_013</t>
+  </si>
+  <si>
+    <t>NSBS_014</t>
+  </si>
+  <si>
+    <t>NSBS_015</t>
+  </si>
+  <si>
+    <t>NSBS_016</t>
+  </si>
+  <si>
+    <t>NSBS_017</t>
+  </si>
+  <si>
+    <t>NSBS_018</t>
+  </si>
+  <si>
+    <t>NSBS_019</t>
+  </si>
+  <si>
+    <t>NSBS_020</t>
+  </si>
+  <si>
+    <t>NSBS_021</t>
+  </si>
+  <si>
+    <t>NSBS_022</t>
+  </si>
+  <si>
+    <t>NSBS_023</t>
+  </si>
+  <si>
+    <t>NSBS_024</t>
+  </si>
+  <si>
+    <t>NSBS_025</t>
+  </si>
+  <si>
+    <t>NSBS_026</t>
+  </si>
+  <si>
+    <t>NSBS_027</t>
+  </si>
+  <si>
+    <t>NSBS_028</t>
+  </si>
+  <si>
+    <t>NSBS_029</t>
+  </si>
+  <si>
+    <t>NSBS_030</t>
+  </si>
+  <si>
+    <t>NSBS_031</t>
+  </si>
+  <si>
+    <t>NWES_001</t>
+  </si>
+  <si>
+    <t>NWES_002</t>
+  </si>
+  <si>
+    <t>NWES_003</t>
+  </si>
+  <si>
+    <t>NWES_004</t>
+  </si>
+  <si>
+    <t>NWES_005</t>
+  </si>
+  <si>
+    <t>NWES_006</t>
+  </si>
+  <si>
+    <t>NWES_007</t>
+  </si>
+  <si>
+    <t>NWES_008</t>
+  </si>
+  <si>
+    <t>NWES_009</t>
+  </si>
+  <si>
+    <t>NWES_010</t>
+  </si>
+  <si>
+    <t>NWES_011</t>
+  </si>
+  <si>
+    <t>NWES_012</t>
+  </si>
+  <si>
+    <t>NWES_013</t>
+  </si>
+  <si>
+    <t>NWES_014</t>
+  </si>
+  <si>
+    <t>NWES_015</t>
+  </si>
+  <si>
+    <t>NWES_016</t>
+  </si>
+  <si>
+    <t>NWES_017</t>
+  </si>
+  <si>
+    <t>BALT_001</t>
+  </si>
+  <si>
+    <t>BALT_002</t>
+  </si>
+  <si>
+    <t>BALT_003</t>
+  </si>
+  <si>
+    <t>BALT_004</t>
+  </si>
+  <si>
+    <t>BALT_005</t>
+  </si>
+  <si>
+    <t>BALT_006</t>
+  </si>
+  <si>
+    <t>BALT_007</t>
+  </si>
+  <si>
+    <t>BALT_008</t>
+  </si>
+  <si>
+    <t>Station Description</t>
+  </si>
+  <si>
+    <t>Cape Desolation Section - Station 3 - Greenland Shelf</t>
+  </si>
+  <si>
+    <t>Fylla Section - Station 4 - Greenland Shelf</t>
+  </si>
+  <si>
+    <t>Nuuk Air Temperature</t>
+  </si>
+  <si>
+    <t>Fyllas Banke - Station 4 - Greenland Shelf</t>
+  </si>
+  <si>
+    <t>Gulf Of St Lawrence</t>
+  </si>
+  <si>
+    <t>Cartwright Air Temperature</t>
+  </si>
+  <si>
+    <t>CIL Layer Newfoundland and Labrador</t>
+  </si>
+  <si>
+    <t>Sea Ice Volume Newfoundland and Labrador</t>
+  </si>
+  <si>
+    <t>Station 27 - Newfoundland Shelf Temperature - Canada</t>
+  </si>
+  <si>
+    <t>Cabot Strait -  - Canada</t>
+  </si>
+  <si>
+    <t>Cabot Strait Sea Ice</t>
+  </si>
+  <si>
+    <t>Emerald Basin - Central Scotian Shelf - Canada</t>
+  </si>
+  <si>
+    <t>Georges Basin -  - Canada</t>
+  </si>
+  <si>
+    <t>Misaine Bank - North East Scotian Shelf - Canada</t>
+  </si>
+  <si>
+    <t>Sable Island Air Temperature</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Eastern Gulf of Maine</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Northeast Channel</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Northern Middle Atlantic Bight</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Northwest Georges Bank</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Southern Middle Atlantic Bight</t>
+  </si>
+  <si>
+    <t>NE US Continental Shelf - Western Gulf of Maine</t>
+  </si>
+  <si>
+    <t>Labrador Shelf - Canada</t>
+  </si>
+  <si>
+    <t>Newfoundland Shelf - Canada</t>
+  </si>
+  <si>
+    <t>Scotian Shelf - Canada</t>
+  </si>
+  <si>
+    <t>Gulf of Maine - Canada</t>
+  </si>
+  <si>
+    <t>Central Irminger Sea</t>
+  </si>
+  <si>
+    <t>East Greenland Slope Denmark Strait Overflow Water</t>
+  </si>
+  <si>
+    <t>Extended Ellett Line - Hatton Rockall Basin</t>
+  </si>
+  <si>
+    <t>Extended Ellett Line - Iceland Basin</t>
+  </si>
+  <si>
+    <t>Area2b HadISST 1.1 SST</t>
+  </si>
+  <si>
+    <t>Extended Ellett Line - Rockall Trough</t>
+  </si>
+  <si>
+    <t>Subpolar North Atlantic - Central Labrador Sea</t>
+  </si>
+  <si>
+    <t>Subpolar North Atlantic - Central Irminger Sea</t>
+  </si>
+  <si>
+    <t>Subpolar North Atlantic - Northern Iceland Basin</t>
+  </si>
+  <si>
+    <t>Subpolar North Atlantic - Central Iceland Basin</t>
+  </si>
+  <si>
+    <t>Subpolar North Atlantic - Rockall Trough</t>
+  </si>
+  <si>
+    <t>Santander Station 6 (Shelf Break) - Bay of Biscay - Spain</t>
+  </si>
+  <si>
+    <t>Santander Station 7 (Outer Slope) - Bay of Biscay - Spain</t>
+  </si>
+  <si>
+    <t>SP6 STOCA - Gulf of Cadiz Time Series</t>
+  </si>
+  <si>
+    <t>Raprocan Section - Canary Basin Coastal Transition Zone (stations 6-10)</t>
+  </si>
+  <si>
+    <t>Raprocan Section - Canary Basin Oceanic Waters (stations 11-24)</t>
+  </si>
+  <si>
+    <t>Finisterre Section - Western Iberian Margin</t>
+  </si>
+  <si>
+    <t>San Sebastian Sea Surface Temperature - Spain</t>
+  </si>
+  <si>
+    <t>Fugloya - Bear Island Section - Western Barents Sea - Atlantic Inflow</t>
+  </si>
+  <si>
+    <t>Kola Section - Eastern Barents Sea</t>
+  </si>
+  <si>
+    <t>VardÃ¸-North Section - Western Barents Sea - Atlantic Inflow</t>
+  </si>
+  <si>
+    <t>Faroe Coastal Skopun</t>
+  </si>
+  <si>
+    <t>Faroe Coastal Oyrargjogv</t>
+  </si>
+  <si>
+    <t>Faroe Bank Channel - West Faroe Islands</t>
+  </si>
+  <si>
+    <t>Faroe Current - North Faroe Islands (Modified North Atlantic Water)</t>
+  </si>
+  <si>
+    <t>Faroe Shetland Channel</t>
+  </si>
+  <si>
+    <t>Faroe Shetland Channel - Faroe Shelf (Modified North Atlantic Water)</t>
+  </si>
+  <si>
+    <t>Faroe Shetland Channel - Shetland Shelf (North Atlantic Water)</t>
+  </si>
+  <si>
+    <t>Fram Strait - East Greenland Current</t>
+  </si>
+  <si>
+    <t>Fram Strait - Return Atlantic Water</t>
+  </si>
+  <si>
+    <t>Fram Strait - West Spitsbergen Current</t>
+  </si>
+  <si>
+    <t>Central Norwegian Sea -  Gimsoy Section - Atlantic Water</t>
+  </si>
+  <si>
+    <t>Norwegian Sea -  Atlantic Water</t>
+  </si>
+  <si>
+    <t>Ocean Weather Station Mike</t>
+  </si>
+  <si>
+    <t>Northern Norwegian Sea - Sorkapp Section - Atlantic Water</t>
+  </si>
+  <si>
+    <t>Southern Norwegian Sea -  Svinoy Section - Atlantic Water</t>
+  </si>
+  <si>
+    <t>Greenland Sea section - West of Spitsbergen 76.5N</t>
+  </si>
+  <si>
+    <t>Akureyri Air Temperature</t>
+  </si>
+  <si>
+    <t>Iceland Deep Data 1800m</t>
+  </si>
+  <si>
+    <t>Reykavik Air Temperature</t>
+  </si>
+  <si>
+    <t>Selvogsbanki Station 5 - South West Iceland - Irminger Current - Spring</t>
+  </si>
+  <si>
+    <t>Siglunes Station 2-4 - North Iceland - North Icelandic Irminger Current - Spring</t>
+  </si>
+  <si>
+    <t>Faxafloi Station 9 - Northern Irminger Sea - Winter</t>
+  </si>
+  <si>
+    <t>Faroe Section N - Station N14 (Deep water)</t>
+  </si>
+  <si>
+    <t>Faroe Section N - Stations N05-N10 (Intermediate water)</t>
+  </si>
+  <si>
+    <t>Faroe Shetland Channel</t>
+  </si>
+  <si>
+    <t>Langanes Station 2-6 - North East Iceland - East Icelandic Current - Spring</t>
+  </si>
+  <si>
+    <t>Eastern Greenland Sea - Atlantic Water</t>
+  </si>
+  <si>
+    <t>Point 33 - Astan</t>
+  </si>
+  <si>
+    <t>M3 Marine Weather Buoy</t>
+  </si>
+  <si>
+    <t>Malin Head Weather Station</t>
+  </si>
+  <si>
+    <t>38a Oceanographic Mooring</t>
+  </si>
+  <si>
+    <t>North Sea - Helgoland Roads</t>
+  </si>
+  <si>
+    <t>North Sea SST</t>
+  </si>
+  <si>
+    <t>Fair Isle Current Water (Waters entering North Sea from Atlantic)</t>
+  </si>
+  <si>
+    <t>Felixstowe-Gabbard - 52N - Ferry merged Smartbuoy</t>
+  </si>
+  <si>
+    <t>Modelled North Sea Inflow</t>
+  </si>
+  <si>
+    <t>North Sea Utsira A</t>
+  </si>
+  <si>
+    <t>North Sea Utsira B</t>
+  </si>
+  <si>
+    <t>Western Channel Observatory (WCO) - E1 - UK</t>
+  </si>
+  <si>
+    <t>Central Skagerrak</t>
+  </si>
+  <si>
+    <t>Cooled Atlantic Water (Atlantic Water below the seasonal thermocline in central Northern North Sea)</t>
+  </si>
+  <si>
+    <t>Baltic Proper - East of Gotland - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Baltic - G2 - Gulf of Gdansk</t>
+  </si>
+  <si>
+    <t>Baltic Proper - SMHI Observed Ice Extent</t>
+  </si>
+  <si>
+    <t>Baltic - LL12 - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Baltic - LL15 - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Baltic - LL7 - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Baltic - SR5 - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Baltic - US5B - Baltic Sea</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>60.47 N</t>
+  </si>
+  <si>
+    <t>63.88 N</t>
+  </si>
+  <si>
+    <t>64.2 N</t>
+  </si>
+  <si>
+    <t>63.88 N</t>
+  </si>
+  <si>
+    <t>48.5 N</t>
+  </si>
+  <si>
+    <t>53.7 N</t>
+  </si>
+  <si>
+    <t>49.5 N</t>
+  </si>
+  <si>
+    <t>50 N</t>
+  </si>
+  <si>
+    <t>47.55 N</t>
+  </si>
+  <si>
+    <t>47.3N</t>
+  </si>
+  <si>
+    <t>46.5 N</t>
+  </si>
+  <si>
+    <t>44 N</t>
+  </si>
+  <si>
+    <t>42.5N</t>
+  </si>
+  <si>
+    <t>45 N</t>
+  </si>
+  <si>
+    <t>43.93 N</t>
+  </si>
+  <si>
+    <t>43 N</t>
+  </si>
+  <si>
+    <t>42.2 N</t>
+  </si>
+  <si>
+    <t>40 N</t>
+  </si>
+  <si>
+    <t>41.5 N</t>
+  </si>
+  <si>
+    <t>38.25 N</t>
+  </si>
+  <si>
+    <t>43 N</t>
+  </si>
+  <si>
+    <t>56.5 N</t>
+  </si>
+  <si>
+    <t>47 N</t>
+  </si>
+  <si>
+    <t>44 N</t>
+  </si>
+  <si>
+    <t>42.5 N</t>
+  </si>
+  <si>
+    <t>59.4 N</t>
+  </si>
+  <si>
+    <t>59.6 N</t>
+  </si>
+  <si>
+    <t>58.66 N</t>
+  </si>
+  <si>
+    <t>60.00 N</t>
+  </si>
+  <si>
+    <t>56.5 N</t>
+  </si>
+  <si>
+    <t>57.5 N</t>
+  </si>
+  <si>
+    <t>57.18 N</t>
+  </si>
+  <si>
+    <t>58.71 N</t>
+  </si>
+  <si>
+    <t>60.01 N</t>
+  </si>
+  <si>
+    <t>57.84 N</t>
+  </si>
+  <si>
+    <t>55.56 N</t>
+  </si>
+  <si>
+    <t>43.708 N</t>
+  </si>
+  <si>
+    <t>43.800 N</t>
+  </si>
+  <si>
+    <t>36.145 N</t>
+  </si>
+  <si>
+    <t>28.5 N</t>
+  </si>
+  <si>
+    <t>29 N</t>
+  </si>
+  <si>
+    <t>43 N</t>
+  </si>
+  <si>
+    <t>43.323 N</t>
+  </si>
+  <si>
+    <t>73 N</t>
+  </si>
+  <si>
+    <t>71.5 N</t>
+  </si>
+  <si>
+    <t>73 N</t>
+  </si>
+  <si>
+    <t>61.91 N</t>
+  </si>
+  <si>
+    <t>62.12 N</t>
+  </si>
+  <si>
+    <t>61.4 N</t>
+  </si>
+  <si>
+    <t>63 N</t>
+  </si>
+  <si>
+    <t>61.25 N</t>
+  </si>
+  <si>
+    <t>61.5 N</t>
+  </si>
+  <si>
+    <t>61 N</t>
+  </si>
+  <si>
+    <t>78.83 N</t>
+  </si>
+  <si>
+    <t>69 N</t>
+  </si>
+  <si>
+    <t>70 N</t>
+  </si>
+  <si>
+    <t>66 N</t>
+  </si>
+  <si>
+    <t>76.33 N</t>
+  </si>
+  <si>
+    <t>63 N</t>
+  </si>
+  <si>
+    <t>76.5 N</t>
+  </si>
+  <si>
+    <t>65.41 N</t>
+  </si>
+  <si>
+    <t>68 N</t>
+  </si>
+  <si>
+    <t>64.08 N</t>
+  </si>
+  <si>
+    <t>63.00 N</t>
+  </si>
+  <si>
+    <t>67 N</t>
+  </si>
+  <si>
+    <t>64.2 N</t>
+  </si>
+  <si>
+    <t>64.5 N</t>
+  </si>
+  <si>
+    <t>63.416 N</t>
+  </si>
+  <si>
+    <t>61.25 N</t>
+  </si>
+  <si>
+    <t>67.5 N</t>
+  </si>
+  <si>
+    <t>75 N</t>
+  </si>
+  <si>
+    <t>48.78 N</t>
+  </si>
+  <si>
+    <t>51.22 N</t>
+  </si>
+  <si>
+    <t>55.37 N</t>
+  </si>
+  <si>
+    <t>53.783 N</t>
+  </si>
+  <si>
+    <t>54.183 N</t>
+  </si>
+  <si>
+    <t>55.99 N</t>
+  </si>
+  <si>
+    <t>59 N</t>
+  </si>
+  <si>
+    <t>52 N</t>
+  </si>
+  <si>
+    <t>59 N</t>
+  </si>
+  <si>
+    <t>50.033 N</t>
+  </si>
+  <si>
+    <t>58.133 N</t>
+  </si>
+  <si>
+    <t>57.933 N</t>
+  </si>
+  <si>
+    <t>58.133 N</t>
+  </si>
+  <si>
+    <t>59 N</t>
+  </si>
+  <si>
+    <t>57.5 N</t>
+  </si>
+  <si>
+    <t>54.833 N</t>
+  </si>
+  <si>
+    <t>65 N</t>
+  </si>
+  <si>
+    <t>59.48 N</t>
+  </si>
+  <si>
+    <t>59.18 N</t>
+  </si>
+  <si>
+    <t>59.85 N</t>
+  </si>
+  <si>
+    <t>61.08 N</t>
+  </si>
+  <si>
+    <t>62.59 N</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>50.00 W</t>
+  </si>
+  <si>
+    <t>53.37 W</t>
+  </si>
+  <si>
+    <t>51.8 W</t>
+  </si>
+  <si>
+    <t>53.37 W</t>
+  </si>
+  <si>
+    <t>61.0 W</t>
+  </si>
+  <si>
+    <t>57.0 W</t>
+  </si>
+  <si>
+    <t>50.5 W</t>
+  </si>
+  <si>
+    <t>50 W</t>
+  </si>
+  <si>
+    <t>52.59 W</t>
+  </si>
+  <si>
+    <t>60.3W</t>
+  </si>
+  <si>
+    <t>58.5 W</t>
+  </si>
+  <si>
+    <t>63 W</t>
+  </si>
+  <si>
+    <t>67W</t>
+  </si>
+  <si>
+    <t>59 W</t>
+  </si>
+  <si>
+    <t>59.97 W</t>
+  </si>
+  <si>
+    <t>67 W</t>
+  </si>
+  <si>
+    <t>66 W</t>
+  </si>
+  <si>
+    <t>71 W</t>
+  </si>
+  <si>
+    <t>68.3 W</t>
+  </si>
+  <si>
+    <t>74.5 W</t>
+  </si>
+  <si>
+    <t>69 W</t>
+  </si>
+  <si>
+    <t>59 W</t>
+  </si>
+  <si>
+    <t>50 W</t>
+  </si>
+  <si>
+    <t>61.5 W</t>
+  </si>
+  <si>
+    <t>69 W</t>
+  </si>
+  <si>
+    <t>36.8 W</t>
+  </si>
+  <si>
+    <t>38.8 W</t>
+  </si>
+  <si>
+    <t>16.50 W</t>
+  </si>
+  <si>
+    <t>20.00 W</t>
+  </si>
+  <si>
+    <t>52.5 W</t>
+  </si>
+  <si>
+    <t>11.00 W</t>
+  </si>
+  <si>
+    <t>51.95 W</t>
+  </si>
+  <si>
+    <t>39.23 W</t>
+  </si>
+  <si>
+    <t>19.67 W</t>
+  </si>
+  <si>
+    <t>25.76 W</t>
+  </si>
+  <si>
+    <t>12.91 W</t>
+  </si>
+  <si>
+    <t>3.786 W</t>
+  </si>
+  <si>
+    <t>3.784 W</t>
+  </si>
+  <si>
+    <t>6.713 W</t>
+  </si>
+  <si>
+    <t>13 W</t>
+  </si>
+  <si>
+    <t>16 W</t>
+  </si>
+  <si>
+    <t>12.15 W</t>
+  </si>
+  <si>
+    <t>1.9922 W</t>
+  </si>
+  <si>
+    <t>20 E</t>
+  </si>
+  <si>
+    <t>33.5 E</t>
+  </si>
+  <si>
+    <t>31.2 E</t>
+  </si>
+  <si>
+    <t>6.88 W</t>
+  </si>
+  <si>
+    <t>7.17 W</t>
+  </si>
+  <si>
+    <t>8.3 W</t>
+  </si>
+  <si>
+    <t>6 W</t>
+  </si>
+  <si>
+    <t>4.5 W</t>
+  </si>
+  <si>
+    <t>6 W</t>
+  </si>
+  <si>
+    <t>3 W</t>
+  </si>
+  <si>
+    <t>6 W</t>
+  </si>
+  <si>
+    <t>1 E</t>
+  </si>
+  <si>
+    <t>7 E</t>
+  </si>
+  <si>
+    <t>12 E</t>
+  </si>
+  <si>
+    <t>0 E</t>
+  </si>
+  <si>
+    <t>2 E</t>
+  </si>
+  <si>
+    <t>10 E</t>
+  </si>
+  <si>
+    <t>3 E</t>
+  </si>
+  <si>
+    <t>10.5 E</t>
+  </si>
+  <si>
+    <t>18.05 W</t>
+  </si>
+  <si>
+    <t>12 W</t>
+  </si>
+  <si>
+    <t>21.54 W</t>
+  </si>
+  <si>
+    <t>21.47 W</t>
+  </si>
+  <si>
+    <t>18 W</t>
+  </si>
+  <si>
+    <t>28 W</t>
+  </si>
+  <si>
+    <t>6 W</t>
+  </si>
+  <si>
+    <t>6.083 W</t>
+  </si>
+  <si>
+    <t>4.5 W</t>
+  </si>
+  <si>
+    <t>13.5 W</t>
+  </si>
+  <si>
+    <t>11.5 E</t>
+  </si>
+  <si>
+    <t>3.94 W</t>
+  </si>
+  <si>
+    <t>10.55 W</t>
+  </si>
+  <si>
+    <t>7.34 W</t>
+  </si>
+  <si>
+    <t>5.625 W</t>
+  </si>
+  <si>
+    <t>7.9 E</t>
+  </si>
+  <si>
+    <t>3.201 E</t>
+  </si>
+  <si>
+    <t>2 W</t>
+  </si>
+  <si>
+    <t>2 E</t>
+  </si>
+  <si>
+    <t>1 E</t>
+  </si>
+  <si>
+    <t>0.5 E</t>
+  </si>
+  <si>
+    <t>4 E</t>
+  </si>
+  <si>
+    <t>4.367 W</t>
+  </si>
+  <si>
+    <t>9.183 E</t>
+  </si>
+  <si>
+    <t>9.450 E</t>
+  </si>
+  <si>
+    <t>9.183 E</t>
+  </si>
+  <si>
+    <t>0.5 W</t>
+  </si>
+  <si>
+    <t>19.5 E</t>
+  </si>
+  <si>
+    <t>19.316 E</t>
+  </si>
+  <si>
+    <t>23 E</t>
+  </si>
+  <si>
+    <t>22.90 E</t>
+  </si>
+  <si>
+    <t>21.75 E</t>
+  </si>
+  <si>
+    <t>24.84 E</t>
+  </si>
+  <si>
+    <t>19.58 E</t>
+  </si>
+  <si>
+    <t>19.97 E</t>
+  </si>
+  <si>
+    <t>Measurement Depth (m)</t>
+  </si>
+  <si>
+    <t>75-200 m</t>
+  </si>
+  <si>
+    <t>2000 m</t>
+  </si>
+  <si>
+    <t>0-50 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>0-50 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Land Surface</t>
+  </si>
+  <si>
+    <t>0-176 m</t>
+  </si>
+  <si>
+    <t>200 - 300 m (Near Bottom)</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>250 m (Near Bottom)</t>
+  </si>
+  <si>
+    <t>200 m (Near Bottom)</t>
+  </si>
+  <si>
+    <t>100 m (Near Bottom)</t>
+  </si>
+  <si>
+    <t>1-30 m</t>
+  </si>
+  <si>
+    <t>150-200 m</t>
+  </si>
+  <si>
+    <t>1-30 m</t>
+  </si>
+  <si>
+    <t>1-30m</t>
+  </si>
+  <si>
+    <t>1-30 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>1600-2000 m</t>
+  </si>
+  <si>
+    <t>200-400 m</t>
+  </si>
+  <si>
+    <t>Near Bottom</t>
+  </si>
+  <si>
+    <t>Upper 800 m</t>
+  </si>
+  <si>
+    <t>Deep Ocean 2000-2700m</t>
+  </si>
+  <si>
+    <t>Intermediate Ocean 1000-2000m</t>
+  </si>
+  <si>
+    <t>Upper Ocean 30-600m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Intermediate Ocean 1500-2300m</t>
+  </si>
+  <si>
+    <t>Upper Ocean 30-800m</t>
+  </si>
+  <si>
+    <t>15-200 m</t>
+  </si>
+  <si>
+    <t>200-1500 m</t>
+  </si>
+  <si>
+    <t>15-200 m</t>
+  </si>
+  <si>
+    <t>200-1500 m</t>
+  </si>
+  <si>
+    <t>15-200 m</t>
+  </si>
+  <si>
+    <t>200-1500 m</t>
+  </si>
+  <si>
+    <t>15-200 m</t>
+  </si>
+  <si>
+    <t>200-1500 m</t>
+  </si>
+  <si>
+    <t>15-200 m</t>
+  </si>
+  <si>
+    <t>200-1500 m</t>
+  </si>
+  <si>
+    <t>0-30 m</t>
+  </si>
+  <si>
+    <t>300-600 m</t>
+  </si>
+  <si>
+    <t>600-950 m</t>
+  </si>
+  <si>
+    <t>0-20 m</t>
+  </si>
+  <si>
+    <t>1-20 m</t>
+  </si>
+  <si>
+    <t>100-300 m</t>
+  </si>
+  <si>
+    <t>300-600 m</t>
+  </si>
+  <si>
+    <t>25-150 dbar</t>
+  </si>
+  <si>
+    <t>200-800 dbar</t>
+  </si>
+  <si>
+    <t>800-1200 dbar</t>
+  </si>
+  <si>
+    <t>200-800 dbar</t>
+  </si>
+  <si>
+    <t>800-1400 dbar</t>
+  </si>
+  <si>
+    <t>1400-2600 dbar</t>
+  </si>
+  <si>
+    <t>2600-3600 dbar</t>
+  </si>
+  <si>
+    <t>200-800m</t>
+  </si>
+  <si>
+    <t>800-2000m</t>
+  </si>
+  <si>
+    <t>2000-5500m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>50-200 m</t>
+  </si>
+  <si>
+    <t>0-200 m</t>
+  </si>
+  <si>
+    <t>50-200 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Upper Layer High Salinity Core</t>
+  </si>
+  <si>
+    <t>800 m</t>
+  </si>
+  <si>
+    <t>Upper Layer - typically between  0-200m</t>
+  </si>
+  <si>
+    <t>50-500 m</t>
+  </si>
+  <si>
+    <t>50-200 m</t>
+  </si>
+  <si>
+    <t>0-800 m</t>
+  </si>
+  <si>
+    <t>2000 m</t>
+  </si>
+  <si>
+    <t>50 m</t>
+  </si>
+  <si>
+    <t>50-200 m</t>
+  </si>
+  <si>
+    <t>200 m</t>
+  </si>
+  <si>
+    <t>1500-1800 m</t>
+  </si>
+  <si>
+    <t>0-200 m</t>
+  </si>
+  <si>
+    <t>50-150 m</t>
+  </si>
+  <si>
+    <t>200-500 m</t>
+  </si>
+  <si>
+    <t>1800-2000 m</t>
+  </si>
+  <si>
+    <t>800-1000 m</t>
+  </si>
+  <si>
+    <t>1000 m</t>
+  </si>
+  <si>
+    <t>1100 m</t>
+  </si>
+  <si>
+    <t>0-50 m</t>
+  </si>
+  <si>
+    <t>50-150 m</t>
+  </si>
+  <si>
+    <t>2 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Seabed</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>0-100 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Depth Averaged</t>
+  </si>
+  <si>
+    <t>Nearbed</t>
+  </si>
+  <si>
+    <t>0-40 m</t>
+  </si>
+  <si>
+    <t>Surface-water</t>
+  </si>
+  <si>
+    <t>Deep-water</t>
+  </si>
+  <si>
+    <t>Bottom-water</t>
+  </si>
+  <si>
+    <t>50-100 m</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>75 m</t>
+  </si>
+  <si>
+    <t>120 m</t>
+  </si>
+  <si>
+    <t>70 m</t>
+  </si>
+  <si>
+    <t>110 m</t>
+  </si>
+  <si>
+    <t>200 m</t>
+  </si>
+  <si>
+    <t>Data Source</t>
+  </si>
+  <si>
+    <t>Thünen-Institut für Seefischerei - Germany - Thünen Institute of Sea Fisheries</t>
+  </si>
+  <si>
+    <t>Danish Meteorological Institute - Copenhagen</t>
+  </si>
+  <si>
+    <t>Greenland Institute of Natural Resources</t>
+  </si>
+  <si>
+    <t>Department of Fisheries and Oceans - Canada</t>
+  </si>
+  <si>
+    <t>Northwest Atlantic Fisheries Centre - Canada</t>
+  </si>
+  <si>
+    <t>Department of Fisheries and Oceans - Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department of Fisheries and Oceans - Canada </t>
+  </si>
+  <si>
+    <t>Department of Fisheries and Oceans - Canada</t>
+  </si>
+  <si>
+    <t>NOAA Fisheries - NEFSC - Oceans and Climate Branch - USA</t>
+  </si>
+  <si>
+    <t>Department of Fisheries and Oceans - Canada</t>
+  </si>
+  <si>
+    <t>Koninklijk Nederlands Instituut voor Zeeonderzoek (NIOZ) - Royal Netherlands Institute for Sea Research</t>
+  </si>
+  <si>
+    <t>National Oceanography Centre and Scottish Association for Marine Science - UK</t>
+  </si>
+  <si>
+    <t>Met Office Hadley Centre - UK</t>
+  </si>
+  <si>
+    <t>National Oceanography Centre and Scottish Association for Marine Science - UK</t>
+  </si>
+  <si>
+    <t>"The Deep-Ocean Observation and Research Synthesis (DOORS). Oceanographic observations included in the DOORS are obtained from multiple sources</t>
+  </si>
+  <si>
+    <t>IEO-CSIC Spanish Institute of Oceanography www.ieo.es - Spain</t>
+  </si>
+  <si>
+    <t>IEO-CSIC - Instituto Espanol de Oceanografia - Spanish Institute of Oceanography - Spain</t>
+  </si>
+  <si>
+    <t>IEO-CSIC Instituto Espanol de Oceanografia - Spanish Institute of Oceanography - Spain</t>
+  </si>
+  <si>
+    <t>IEO - Instituto Espanol de Oceanografia - Spanish Institute of Oceanography - Spain</t>
+  </si>
+  <si>
+    <t>IEO-CSIC - Instituto Espanol de Oceanografia - Spanish Institute of Oceanography - Spain</t>
+  </si>
+  <si>
+    <t>Aquarium of San Sebastian (Oceanographic Society of Gipuzkoa and Oceanographic Foundation of Gipuzkoa) - Spain</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>PINRO - Polar Branch of the Russian Federal Research Institute of Fisheries and Oceanography - Russia</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>Havstovan - Faroe - Faroe Marine Research Institute</t>
+  </si>
+  <si>
+    <t>SGMD - Scottish Government Marine Directorate - Aberdeen - UK</t>
+  </si>
+  <si>
+    <t>AWI - Alfred Wegener Institute for Polar and Marine Research - Germany and NPI - Norwegian Polar Institute - Norway</t>
+  </si>
+  <si>
+    <t>AWI - Alfred Wegener Institute for Polar and Marine Research - Germany and IOPAN - Institute of Oceanology Polish Academy of Sciences - Poland</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>Institut of Marine Research Bergen - Norway</t>
+  </si>
+  <si>
+    <t>Geophysical Institute - University of Bergen - Norway</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>IOPAS - Institute of Oceanology Polish Academy of Sciences - Poland</t>
+  </si>
+  <si>
+    <t>Hafrannsoknastofnun - Iceland - IcelandicMetoffice via Marine Research Institute</t>
+  </si>
+  <si>
+    <t>Hafrannsoknastofnun - Iceland - Marine Research Institute</t>
+  </si>
+  <si>
+    <t>Hafrannsoknastofnun - Iceland - Icelandic Metoffice via Marine Research Institute</t>
+  </si>
+  <si>
+    <t>Hafrannsoknastofnun - Iceland - Marine Research Institute</t>
+  </si>
+  <si>
+    <t>Havstovan - Faroe - Faroe Marine Research Institute</t>
+  </si>
+  <si>
+    <t>SGMD - Scottish Government Marine Directorate - Aberdeen - UK</t>
+  </si>
+  <si>
+    <t>Hafrannsoknastofnun - Iceland - Marine Research Institute</t>
+  </si>
+  <si>
+    <t>AWI - Alfred Wegener Institute for Polar and Marine Research - Germany and IOPAN - Institute of Oceanology Polish Academy of Sciences - Poland</t>
+  </si>
+  <si>
+    <t>CNRS - Observatoire Oceanologique de Roscoff - France</t>
+  </si>
+  <si>
+    <t>Marine Institute Ireland</t>
+  </si>
+  <si>
+    <t>Marine Institute/Met Eireann - Ireland</t>
+  </si>
+  <si>
+    <t>AFBI Northern Ireland</t>
+  </si>
+  <si>
+    <t>Alfred-Wegener-Institut (AWI) - Helmholtz-Zentrum für Polar- und Meeresforschung</t>
+  </si>
+  <si>
+    <t>BSH - German Federal Maritime and Hydrographic Agency</t>
+  </si>
+  <si>
+    <t>SGMD - Scottish Government Marine Directorate - Aberdeen - UK</t>
+  </si>
+  <si>
+    <t>CEFAS - Centre for Environment Fisheries and Aquaculture Science - UK</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>Marine Biological Association and Plymouth Marine Laboratory - UK</t>
+  </si>
+  <si>
+    <t>IMR - Institute of Marine Research - Norway</t>
+  </si>
+  <si>
+    <t>SGMD - Scottish Government Marine Directorate - Aberdeen - UK</t>
+  </si>
+  <si>
+    <t>SMHI - Swedish Meteorological and Hydrological Institute</t>
+  </si>
+  <si>
+    <t>National Marine Fisheries Research Institute - Poland (MIR-PIB)</t>
+  </si>
+  <si>
+    <t>SMHI - Swedish Meteorological and Hydrological Institute</t>
+  </si>
+  <si>
+    <t>FMI - Finnish Meteorological Institute - Finland</t>
+  </si>
+  <si>
+    <t>Contact Name</t>
+  </si>
+  <si>
+    <t>Boris Cisewski (boris.cisewski@thuenen.de)</t>
+  </si>
+  <si>
+    <t>John Mortensen (jomo@natur.gl)</t>
+  </si>
+  <si>
+    <t>Peter Galbraith (Peter.Galbraith@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Jonathan Coyne (Jonathan.Coyne@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Jonathna Coyne (Jonathan.Coyne@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Jonathan Coyne (Jonathan.Coyne@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Chantelle Layton (Chantelle.Layton@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>David Hebert (David.Hebert@dfo-mpo.gc.ca);Chantelle Layton (Chantelle.Layton@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Chantelle Layton (Chantelle.Layton@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Paula Fratantoni (paula.fratantoni@noaa.gov)</t>
+  </si>
+  <si>
+    <t>Peter Galbraith (Peter.Galbraith@dfo-mpo.gc.ca)</t>
+  </si>
+  <si>
+    <t>Femke de Jong (femke.de.jong@nioz.nl)</t>
+  </si>
+  <si>
+    <t>Sam Jones (sam.jones@sams.ac.uk)</t>
+  </si>
+  <si>
+    <t>Bee Berx &amp; Berit Rabe (MD.Oceanography@gov.scot)</t>
+  </si>
+  <si>
+    <t>Sam Jones (sam.jones@sams.ac.uk)</t>
+  </si>
+  <si>
+    <t>"Igor Yashayaev (Igor.Yashayaev@dfo-mpo.gc.ca)"</t>
+  </si>
+  <si>
+    <t>Cesar Gonzalez-Pola (cesar.pola@ieo.csic.es)</t>
+  </si>
+  <si>
+    <t>Ricardo F. Sanchez Leal (rleal@ieo.csic.es)</t>
+  </si>
+  <si>
+    <t>Angela Mosquera Gimenez (angela.mosquera@ieo.csic.es);Pedro Velez Belchi (pedro.velez@ieo.csic.es)</t>
+  </si>
+  <si>
+    <t>Angela Mosquera Gimenez (angela.mosquera@ieo.csic.es);Pedro Velez Belchi (pedro.velez@ieo.es)</t>
+  </si>
+  <si>
+    <t>Angela Mosquera Gimenez (angela.mosquera@ieo.csic.es);Pedro Velez Belchi (pedro.velez@ieo.csic.es)</t>
+  </si>
+  <si>
+    <t>Angela Mosquera Gimenez (angela.mosquera@ieo.csic.es);Pedro Velez Belchi (pedro.velez@ieo.es)</t>
+  </si>
+  <si>
+    <t>Cesar Gonzalez-Pola (cesar.pola@ieo.csic.es)</t>
+  </si>
+  <si>
+    <t>Almudena Fontan (afontan@azti.es)</t>
+  </si>
+  <si>
+    <t>Randi Ingvaldsen (randi.ingvaldsen@imr.no)</t>
+  </si>
+  <si>
+    <t>Alexander G. Trofimov (trofimov@pinro.ru)</t>
+  </si>
+  <si>
+    <t>Randi Ingvaldsen (randi.ingvaldsen@imr.no)</t>
+  </si>
+  <si>
+    <t>Karin Margretha H. Larsen (KarinL@hav.fo)</t>
+  </si>
+  <si>
+    <t>Bee Berx &amp; Berit Rabe (MD.Oceanography@gov.scot)</t>
+  </si>
+  <si>
+    <t>Wilken Jon von Appen (wjvappen@awi.de) and Paul Dodd (Paul.Dodd@npi.no)</t>
+  </si>
+  <si>
+    <t>Wilken Jon von Appen (wjvappen@awi.de) and Agnieszka Beszczynska-M_ller (abesz@iopan.gda.pl)</t>
+  </si>
+  <si>
+    <t>Kjell Arne Mork (kjell.arne.mork@imr.no)</t>
+  </si>
+  <si>
+    <t>Svein Ã˜sterhus (Svein.Osterhus@norceresearch.no)</t>
+  </si>
+  <si>
+    <t>Svein Osterhus (Svein.Osterhus@gfi.uib.no)</t>
+  </si>
+  <si>
+    <t>Kjell Arne Mork (kjell.arne.mork@imr.no)</t>
+  </si>
+  <si>
+    <t>Waldemar Walczowski (walczows@iopan.gda.pl)</t>
+  </si>
+  <si>
+    <t>Solveig R. Olafsdottir (solveig.rosa.olafsdottir@hafogvatn.is)</t>
+  </si>
+  <si>
+    <t>Karin Margretha H. Larsen (KarinL@hav.fo)</t>
+  </si>
+  <si>
+    <t>Bee Berx &amp; Berit Rabe (MD.Oceanography@gov.scot)</t>
+  </si>
+  <si>
+    <t>Solveig R. Olafsdottir (solveig.rosa.olafsdottir@hafogvatn.is)</t>
+  </si>
+  <si>
+    <t>Wilken Jon von Appen (wjvappen@awi.de) and Agnieszka Beszczynska-MÃ¶ller (abesz@iopan.pl)</t>
   </si>
   <si>
     <t>Pascal Morin (pmorin@sb-roscoff.fr)</t>
@@ -1801,2865 +5593,3177 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="true"/>
     <col min="2" max="2" width="10.42578125" customWidth="true"/>
     <col min="3" max="3" width="90.42578125" customWidth="true"/>
-    <col min="4" max="4" width="100.5703125" customWidth="true"/>
+    <col min="4" max="4" width="8.5703125" customWidth="true"/>
     <col min="5" max="5" width="10" customWidth="true"/>
     <col min="6" max="6" width="36.42578125" customWidth="true"/>
-    <col min="7" max="7" width="129.7109375" customWidth="true"/>
+    <col min="7" max="7" width="135.140625" customWidth="true"/>
     <col min="8" max="8" width="93.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>1213</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>8</v>
+        <v>1221</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>116</v>
+        <v>1341</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>203</v>
+        <v>1437</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>289</v>
+        <v>1531</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>379</v>
+        <v>1629</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>471</v>
+        <v>1730</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>526</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1</v>
+        <v>1214</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>9</v>
+        <v>1222</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>117</v>
+        <v>1342</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>204</v>
+        <v>1438</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>290</v>
+        <v>1532</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>380</v>
+        <v>1630</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>472</v>
+        <v>1731</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>527</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1</v>
+        <v>1214</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>10</v>
+        <v>1223</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>117</v>
+        <v>1342</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>204</v>
+        <v>1438</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>290</v>
+        <v>1532</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>381</v>
+        <v>1631</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>472</v>
+        <v>1731</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>527</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1</v>
+        <v>1214</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>11</v>
+        <v>1224</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>118</v>
+        <v>1343</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>205</v>
+        <v>1439</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>291</v>
+        <v>1533</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>382</v>
+        <v>1632</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>472</v>
+        <v>1731</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>527</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1</v>
+        <v>1214</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>12</v>
+        <v>1225</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>119</v>
+        <v>1344</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>206</v>
+        <v>1440</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>292</v>
+        <v>1534</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>383</v>
+        <v>1633</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>473</v>
+        <v>1732</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>527</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1</v>
+        <v>1214</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>13</v>
+        <v>1226</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>120</v>
+        <v>1345</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>207</v>
+        <v>1441</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>293</v>
+        <v>1535</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>384</v>
+        <v>1634</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>474</v>
+        <v>1733</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>528</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1</v>
+        <v>1215</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>14</v>
+        <v>1227</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>121</v>
+        <v>1346</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>208</v>
+        <v>1442</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>294</v>
+        <v>1536</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>385</v>
+        <v>1635</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>475</v>
+        <v>1734</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>529</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>15</v>
+        <v>1228</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>122</v>
+        <v>1347</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>209</v>
+        <v>1443</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>295</v>
+        <v>1537</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>386</v>
+        <v>1636</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>476</v>
+        <v>1735</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>530</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>16</v>
+        <v>1229</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>123</v>
+        <v>1348</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>210</v>
+        <v>1444</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>296</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>387</v>
-      </c>
+        <v>1538</v>
+      </c>
+      <c r="F9" s="0"/>
       <c r="G9" s="0" t="s">
-        <v>477</v>
+        <v>1735</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>531</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>1230</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>124</v>
+        <v>1349</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>211</v>
+        <v>1445</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>297</v>
+        <v>1539</v>
       </c>
       <c r="F10" s="0"/>
       <c r="G10" s="0" t="s">
-        <v>477</v>
+        <v>1735</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>532</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>18</v>
+        <v>1231</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>125</v>
+        <v>1350</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>212</v>
+        <v>1446</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>298</v>
-      </c>
-      <c r="F11" s="0"/>
+        <v>1540</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>1637</v>
+      </c>
       <c r="G11" s="0" t="s">
-        <v>477</v>
+        <v>1735</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>533</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>19</v>
+        <v>1232</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>126</v>
+        <v>1351</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>213</v>
+        <v>1447</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>299</v>
+        <v>1541</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>388</v>
+        <v>1638</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>477</v>
+        <v>1736</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>533</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>20</v>
+        <v>1233</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>127</v>
+        <v>1352</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>214</v>
+        <v>1448</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>300</v>
+        <v>1542</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>389</v>
+        <v>1639</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>478</v>
+        <v>1736</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>534</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>21</v>
+        <v>1234</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>128</v>
+        <v>1353</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>215</v>
+        <v>1449</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>301</v>
+        <v>1543</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>390</v>
+        <v>1640</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>478</v>
+        <v>1737</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>534</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>22</v>
+        <v>1235</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>129</v>
+        <v>1354</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>216</v>
+        <v>1450</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>302</v>
+        <v>1544</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>391</v>
+        <v>1641</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>478</v>
+        <v>1738</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>534</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>23</v>
+        <v>1236</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>130</v>
+        <v>1355</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>217</v>
+        <v>1451</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>303</v>
+        <v>1545</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>392</v>
+        <v>1642</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>478</v>
+        <v>1738</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>534</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>24</v>
+        <v>1237</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>131</v>
+        <v>1356</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>218</v>
+        <v>1452</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="F17" s="0" t="s">
-        <v>393</v>
-      </c>
+        <v>1546</v>
+      </c>
+      <c r="F17" s="0"/>
       <c r="G17" s="0" t="s">
-        <v>478</v>
+        <v>1738</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>534</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>25</v>
+        <v>1238</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>132</v>
+        <v>1357</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>219</v>
+        <v>1453</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="F18" s="0"/>
+        <v>1547</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>1643</v>
+      </c>
       <c r="G18" s="0" t="s">
-        <v>478</v>
+        <v>1739</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>535</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>26</v>
+        <v>1239</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>133</v>
+        <v>1358</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>220</v>
+        <v>1454</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>306</v>
+        <v>1548</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>394</v>
+        <v>1644</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>479</v>
+        <v>1739</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>536</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>27</v>
+        <v>1240</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>134</v>
+        <v>1359</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>221</v>
+        <v>1455</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>307</v>
+        <v>1549</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>395</v>
+        <v>1645</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>479</v>
+        <v>1739</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>536</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>28</v>
+        <v>1241</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>135</v>
+        <v>1360</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>222</v>
+        <v>1456</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>308</v>
+        <v>1550</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>396</v>
+        <v>1645</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>479</v>
+        <v>1739</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>536</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>29</v>
+        <v>1242</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>136</v>
+        <v>1361</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>223</v>
+        <v>1457</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>309</v>
+        <v>1551</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>396</v>
+        <v>1646</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>479</v>
+        <v>1739</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>536</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>30</v>
+        <v>1243</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>137</v>
+        <v>1362</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>224</v>
+        <v>1458</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>310</v>
+        <v>1552</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>397</v>
+        <v>1647</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>479</v>
+        <v>1739</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>536</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>31</v>
+        <v>1244</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>138</v>
+        <v>1363</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>225</v>
+        <v>1459</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>311</v>
+        <v>1553</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>398</v>
+        <v>1648</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>479</v>
+        <v>1740</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>536</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>3</v>
+        <v>1215</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>32</v>
+        <v>1245</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>139</v>
+        <v>1364</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>226</v>
+        <v>1460</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>312</v>
+        <v>1554</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>399</v>
+        <v>1648</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>480</v>
+        <v>1740</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>537</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>3</v>
+        <v>1215</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>33</v>
+        <v>1246</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>139</v>
+        <v>1365</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>226</v>
+        <v>1461</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>312</v>
+        <v>1555</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>400</v>
+        <v>1648</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>480</v>
+        <v>1740</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>537</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>3</v>
+        <v>1215</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>34</v>
+        <v>1247</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>140</v>
+        <v>1366</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>227</v>
+        <v>1462</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>313</v>
+        <v>1556</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>401</v>
+        <v>1648</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>480</v>
+        <v>1740</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>537</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>3</v>
+        <v>1216</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>35</v>
+        <v>1248</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>141</v>
+        <v>1367</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>228</v>
+        <v>1463</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>314</v>
+        <v>1557</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>402</v>
+        <v>1649</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>481</v>
+        <v>1741</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>538</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>3</v>
+        <v>1216</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>36</v>
+        <v>1249</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>142</v>
+        <v>1367</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>229</v>
+        <v>1463</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>315</v>
+        <v>1557</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>403</v>
+        <v>1650</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>481</v>
+        <v>1741</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>538</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>3</v>
+        <v>1216</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>37</v>
+        <v>1250</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>142</v>
+        <v>1368</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>229</v>
+        <v>1464</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>315</v>
+        <v>1558</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>404</v>
+        <v>1651</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>481</v>
+        <v>1741</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>538</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>3</v>
+        <v>1216</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>38</v>
+        <v>1251</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>142</v>
+        <v>1369</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>229</v>
+        <v>1465</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>315</v>
+        <v>1559</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>405</v>
+        <v>1652</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>481</v>
+        <v>1742</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>538</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>3</v>
+        <v>1216</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>39</v>
+        <v>1252</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>143</v>
+        <v>1370</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>230</v>
+        <v>1466</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>316</v>
+        <v>1560</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>406</v>
+        <v>1653</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>482</v>
+        <v>1742</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>539</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>3</v>
+        <v>1216</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>40</v>
+        <v>1253</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>143</v>
+        <v>1370</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>230</v>
+        <v>1466</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>316</v>
+        <v>1560</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>407</v>
+        <v>1654</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>482</v>
+        <v>1742</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>539</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>3</v>
+        <v>1216</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>41</v>
+        <v>1254</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>144</v>
+        <v>1370</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>231</v>
+        <v>1466</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>317</v>
+        <v>1560</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>408</v>
+        <v>1655</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>483</v>
+        <v>1742</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>540</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>3</v>
+        <v>1216</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>42</v>
+        <v>1255</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>145</v>
+        <v>1371</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>232</v>
+        <v>1467</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>318</v>
+        <v>1561</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>409</v>
+        <v>1656</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>484</v>
+        <v>1743</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>541</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>3</v>
+        <v>1216</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>43</v>
+        <v>1256</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>145</v>
+        <v>1372</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>232</v>
+        <v>1468</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>318</v>
+        <v>1562</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>410</v>
+        <v>1657</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>484</v>
+        <v>1744</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>541</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>44</v>
+        <v>1257</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>146</v>
+        <v>1372</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>233</v>
+        <v>1468</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>319</v>
+        <v>1562</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>411</v>
+        <v>1658</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>485</v>
+        <v>1744</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>542</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>45</v>
+        <v>1258</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>146</v>
+        <v>1373</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>234</v>
+        <v>1469</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>320</v>
+        <v>1563</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>412</v>
+        <v>1659</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>486</v>
+        <v>1745</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>543</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>46</v>
+        <v>1259</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>147</v>
+        <v>1373</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>235</v>
+        <v>1469</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>321</v>
+        <v>1563</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>413</v>
+        <v>1660</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>487</v>
+        <v>1745</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>543</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>47</v>
+        <v>1260</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>147</v>
+        <v>1374</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>235</v>
+        <v>1470</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>321</v>
+        <v>1564</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>414</v>
+        <v>1661</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>488</v>
+        <v>1745</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>543</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>48</v>
+        <v>1261</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>148</v>
+        <v>1374</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>236</v>
+        <v>1470</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>322</v>
+        <v>1564</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>415</v>
+        <v>1662</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>489</v>
+        <v>1745</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>544</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>48</v>
+        <v>1262</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>148</v>
+        <v>1375</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>236</v>
+        <v>1471</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>322</v>
+        <v>1565</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>416</v>
+        <v>1663</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>489</v>
+        <v>1745</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>544</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>49</v>
+        <v>1263</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>148</v>
+        <v>1375</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>236</v>
+        <v>1471</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>322</v>
+        <v>1565</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>417</v>
+        <v>1664</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>489</v>
+        <v>1745</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>544</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>50</v>
+        <v>1264</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>148</v>
+        <v>1376</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>236</v>
+        <v>1472</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>322</v>
+        <v>1566</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>418</v>
+        <v>1665</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>489</v>
+        <v>1745</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>544</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>51</v>
+        <v>1265</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>149</v>
+        <v>1376</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>237</v>
+        <v>1472</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>323</v>
+        <v>1566</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>419</v>
+        <v>1666</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>489</v>
+        <v>1745</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>545</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>52</v>
+        <v>1266</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>149</v>
+        <v>1377</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>237</v>
+        <v>1473</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>323</v>
+        <v>1567</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>420</v>
+        <v>1667</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>489</v>
+        <v>1745</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>546</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>4</v>
+        <v>1216</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>53</v>
+        <v>1267</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>149</v>
+        <v>1377</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>237</v>
+        <v>1473</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>323</v>
+        <v>1567</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>421</v>
+        <v>1668</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>489</v>
+        <v>1745</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>547</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>4</v>
+        <v>1217</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>54</v>
+        <v>1268</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>150</v>
+        <v>1378</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>238</v>
+        <v>1474</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>324</v>
+        <v>1568</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>422</v>
+        <v>1669</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>489</v>
+        <v>1746</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>547</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>4</v>
+        <v>1217</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>55</v>
+        <v>1269</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>150</v>
+        <v>1379</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>238</v>
+        <v>1475</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>324</v>
+        <v>1569</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>423</v>
+        <v>1670</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>489</v>
+        <v>1747</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>547</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>4</v>
+        <v>1217</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>56</v>
+        <v>1270</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>150</v>
+        <v>1379</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>238</v>
+        <v>1475</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>324</v>
+        <v>1569</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>424</v>
+        <v>1671</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>489</v>
+        <v>1748</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>547</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>4</v>
+        <v>1217</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>57</v>
+        <v>1271</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>150</v>
+        <v>1380</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>238</v>
+        <v>1476</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>324</v>
+        <v>1570</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>425</v>
+        <v>1672</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>489</v>
+        <v>1749</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>548</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>4</v>
+        <v>1217</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>58</v>
+        <v>1271</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>151</v>
+        <v>1380</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>239</v>
+        <v>1476</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>325</v>
+        <v>1570</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>426</v>
+        <v>1673</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>490</v>
+        <v>1749</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>549</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>4</v>
+        <v>1217</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>59</v>
+        <v>1272</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>151</v>
+        <v>1380</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>239</v>
+        <v>1476</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>325</v>
+        <v>1570</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>427</v>
+        <v>1674</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>490</v>
+        <v>1749</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>549</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>4</v>
+        <v>1217</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>60</v>
+        <v>1273</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>151</v>
+        <v>1380</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>239</v>
+        <v>1476</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>325</v>
+        <v>1570</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>428</v>
+        <v>1675</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>490</v>
+        <v>1749</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>549</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>61</v>
+        <v>1274</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>152</v>
+        <v>1381</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>240</v>
+        <v>1477</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>326</v>
+        <v>1571</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>429</v>
+        <v>1676</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>491</v>
+        <v>1749</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>550</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>62</v>
+        <v>1275</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>153</v>
+        <v>1381</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>241</v>
+        <v>1477</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>327</v>
+        <v>1571</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>430</v>
+        <v>1677</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>492</v>
+        <v>1749</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>551</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>63</v>
+        <v>1276</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>154</v>
+        <v>1381</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>242</v>
+        <v>1477</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>328</v>
+        <v>1571</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>431</v>
+        <v>1678</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>493</v>
+        <v>1749</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>552</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>64</v>
+        <v>1277</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>155</v>
+        <v>1382</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>243</v>
+        <v>1478</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>329</v>
+        <v>1572</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>432</v>
+        <v>1679</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>494</v>
+        <v>1749</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>553</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>64</v>
+        <v>1278</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>156</v>
+        <v>1382</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>244</v>
+        <v>1478</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>330</v>
+        <v>1572</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>432</v>
+        <v>1680</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>494</v>
+        <v>1749</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>553</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>65</v>
+        <v>1279</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>157</v>
+        <v>1382</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>245</v>
+        <v>1478</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>331</v>
+        <v>1572</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>433</v>
+        <v>1681</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>494</v>
+        <v>1749</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>553</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>66</v>
+        <v>1280</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>158</v>
+        <v>1382</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>246</v>
+        <v>1478</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>332</v>
+        <v>1572</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>433</v>
+        <v>1682</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>494</v>
+        <v>1749</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>553</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>67</v>
+        <v>1281</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>159</v>
+        <v>1383</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>247</v>
+        <v>1479</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>333</v>
+        <v>1573</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>434</v>
+        <v>1683</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>495</v>
+        <v>1750</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>554</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>68</v>
+        <v>1282</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>160</v>
+        <v>1383</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>248</v>
+        <v>1479</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>334</v>
+        <v>1573</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>435</v>
+        <v>1684</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>495</v>
+        <v>1750</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>554</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>69</v>
+        <v>1283</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>161</v>
+        <v>1383</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>249</v>
+        <v>1479</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>335</v>
+        <v>1573</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>435</v>
+        <v>1685</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>495</v>
+        <v>1750</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>554</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>5</v>
+        <v>1217</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>70</v>
+        <v>1284</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>162</v>
+        <v>1384</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>250</v>
+        <v>1480</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>336</v>
+        <v>1574</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>436</v>
+        <v>1686</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>496</v>
+        <v>1751</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>555</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>71</v>
+        <v>1285</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>163</v>
+        <v>1385</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>250</v>
+        <v>1481</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>337</v>
+        <v>1575</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>436</v>
+        <v>1687</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>496</v>
+        <v>1752</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>555</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>72</v>
+        <v>1286</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>164</v>
+        <v>1386</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>250</v>
+        <v>1482</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>338</v>
+        <v>1576</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>436</v>
+        <v>1688</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>497</v>
+        <v>1753</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>556</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>73</v>
+        <v>1287</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>165</v>
+        <v>1387</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>251</v>
+        <v>1483</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>339</v>
+        <v>1577</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>437</v>
+        <v>1689</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>498</v>
+        <v>1754</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>557</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>74</v>
+        <v>1288</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>166</v>
+        <v>1388</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>252</v>
+        <v>1484</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>340</v>
+        <v>1578</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>438</v>
+        <v>1690</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>498</v>
+        <v>1755</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>557</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>75</v>
+        <v>1288</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>167</v>
+        <v>1389</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>253</v>
+        <v>1485</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>341</v>
+        <v>1579</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>439</v>
+        <v>1690</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>499</v>
+        <v>1755</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>558</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>76</v>
+        <v>1289</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>167</v>
+        <v>1390</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>253</v>
+        <v>1486</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>341</v>
+        <v>1580</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>440</v>
+        <v>1691</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>500</v>
+        <v>1755</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>559</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>77</v>
+        <v>1290</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>168</v>
+        <v>1391</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>254</v>
+        <v>1487</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>342</v>
+        <v>1581</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>441</v>
+        <v>1691</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>501</v>
+        <v>1755</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>560</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>78</v>
+        <v>1291</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>169</v>
+        <v>1392</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>255</v>
+        <v>1488</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>343</v>
+        <v>1582</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>441</v>
+        <v>1692</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>501</v>
+        <v>1756</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>560</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>79</v>
+        <v>1292</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>170</v>
+        <v>1393</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>256</v>
+        <v>1489</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>344</v>
+        <v>1583</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>442</v>
+        <v>1693</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>502</v>
+        <v>1756</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>561</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>80</v>
+        <v>1293</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>171</v>
+        <v>1394</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>257</v>
+        <v>1490</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="F75" s="0"/>
+        <v>1584</v>
+      </c>
+      <c r="F75" s="0" t="s">
+        <v>1693</v>
+      </c>
       <c r="G75" s="0" t="s">
-        <v>503</v>
+        <v>1756</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>562</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>81</v>
+        <v>1294</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>172</v>
+        <v>1395</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>258</v>
+        <v>1491</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>346</v>
+        <v>1585</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>443</v>
+        <v>1694</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>504</v>
+        <v>1757</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>562</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>82</v>
+        <v>1295</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>173</v>
+        <v>1396</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>259</v>
+        <v>1491</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="F77" s="0"/>
+        <v>1586</v>
+      </c>
+      <c r="F77" s="0" t="s">
+        <v>1694</v>
+      </c>
       <c r="G77" s="0" t="s">
-        <v>505</v>
+        <v>1757</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>562</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>83</v>
+        <v>1296</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>174</v>
+        <v>1397</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>260</v>
+        <v>1491</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>348</v>
+        <v>1587</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>444</v>
+        <v>1694</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>506</v>
+        <v>1758</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>562</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>84</v>
+        <v>1297</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>175</v>
+        <v>1398</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>261</v>
+        <v>1492</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>349</v>
+        <v>1588</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>445</v>
+        <v>1695</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>506</v>
+        <v>1759</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>562</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>85</v>
+        <v>1298</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>176</v>
+        <v>1399</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>262</v>
+        <v>1493</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>350</v>
+        <v>1589</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>446</v>
+        <v>1696</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>506</v>
+        <v>1759</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>562</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>86</v>
+        <v>1299</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>177</v>
+        <v>1400</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>263</v>
+        <v>1494</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>351</v>
+        <v>1590</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>447</v>
+        <v>1697</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>507</v>
+        <v>1760</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>563</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>87</v>
+        <v>1300</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>178</v>
+        <v>1400</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>264</v>
+        <v>1494</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>352</v>
+        <v>1590</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>448</v>
+        <v>1698</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>507</v>
+        <v>1761</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>563</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>88</v>
+        <v>1301</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>179</v>
+        <v>1401</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>265</v>
+        <v>1495</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>353</v>
+        <v>1591</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>449</v>
+        <v>1699</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>508</v>
+        <v>1762</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>564</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>89</v>
+        <v>1302</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>179</v>
+        <v>1402</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>265</v>
+        <v>1496</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>353</v>
+        <v>1592</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>450</v>
+        <v>1699</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>508</v>
+        <v>1762</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>564</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>5</v>
+        <v>1218</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>90</v>
+        <v>1303</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>180</v>
+        <v>1403</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>266</v>
+        <v>1497</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>354</v>
+        <v>1593</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>451</v>
+        <v>1700</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>509</v>
+        <v>1763</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>565</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>91</v>
+        <v>1304</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>181</v>
+        <v>1404</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>267</v>
+        <v>1498</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>355</v>
-      </c>
-      <c r="F86" s="0" t="s">
-        <v>452</v>
-      </c>
+        <v>1594</v>
+      </c>
+      <c r="F86" s="0"/>
       <c r="G86" s="0" t="s">
-        <v>510</v>
+        <v>1764</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>566</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>92</v>
+        <v>1305</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>182</v>
+        <v>1405</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>268</v>
+        <v>1499</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>356</v>
+        <v>1595</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>453</v>
+        <v>1701</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>511</v>
+        <v>1765</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>567</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>93</v>
+        <v>1306</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>183</v>
+        <v>1406</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>269</v>
+        <v>1500</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>357</v>
-      </c>
-      <c r="F88" s="0" t="s">
-        <v>453</v>
-      </c>
+        <v>1596</v>
+      </c>
+      <c r="F88" s="0"/>
       <c r="G88" s="0" t="s">
-        <v>512</v>
+        <v>1766</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>567</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>94</v>
+        <v>1307</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>184</v>
+        <v>1407</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>270</v>
+        <v>1501</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>358</v>
+        <v>1597</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>454</v>
+        <v>1702</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>513</v>
+        <v>1767</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>568</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>95</v>
+        <v>1308</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>184</v>
+        <v>1408</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>270</v>
+        <v>1502</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>358</v>
+        <v>1598</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>455</v>
+        <v>1703</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>513</v>
+        <v>1767</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>568</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>96</v>
+        <v>1309</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>185</v>
+        <v>1409</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>271</v>
+        <v>1503</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>359</v>
+        <v>1599</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>455</v>
+        <v>1704</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>514</v>
+        <v>1767</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>569</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>97</v>
+        <v>1310</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>186</v>
+        <v>1410</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>272</v>
+        <v>1504</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>360</v>
+        <v>1600</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>455</v>
+        <v>1705</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>515</v>
+        <v>1768</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>570</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>98</v>
+        <v>1311</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>187</v>
+        <v>1411</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>273</v>
+        <v>1505</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>361</v>
+        <v>1601</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>456</v>
+        <v>1706</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>516</v>
+        <v>1768</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>571</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>99</v>
+        <v>1312</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>188</v>
+        <v>1412</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>274</v>
+        <v>1506</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>362</v>
+        <v>1602</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>457</v>
+        <v>1707</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>517</v>
+        <v>1769</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>572</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>100</v>
+        <v>1313</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>189</v>
+        <v>1412</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>275</v>
+        <v>1506</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>363</v>
+        <v>1602</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>458</v>
+        <v>1708</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>518</v>
+        <v>1769</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>573</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>101</v>
+        <v>1314</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>190</v>
+        <v>1413</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>275</v>
+        <v>1507</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>364</v>
+        <v>1603</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>459</v>
+        <v>1709</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>518</v>
+        <v>1770</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>573</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>6</v>
+        <v>1218</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>102</v>
+        <v>1315</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>191</v>
+        <v>1414</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>275</v>
+        <v>1508</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="F97" s="0"/>
+        <v>1604</v>
+      </c>
+      <c r="F97" s="0" t="s">
+        <v>1710</v>
+      </c>
       <c r="G97" s="0" t="s">
-        <v>518</v>
+        <v>1771</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>573</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>6</v>
+        <v>1219</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>103</v>
+        <v>1316</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>192</v>
+        <v>1415</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>276</v>
+        <v>1509</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>366</v>
+        <v>1605</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>460</v>
+        <v>1711</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>519</v>
+        <v>1772</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>574</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>6</v>
+        <v>1219</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>104</v>
+        <v>1317</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>193</v>
+        <v>1416</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>277</v>
+        <v>1510</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>367</v>
+        <v>1606</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>461</v>
+        <v>1712</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>520</v>
+        <v>1773</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>575</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>6</v>
+        <v>1219</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>105</v>
+        <v>1318</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>193</v>
+        <v>1417</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>278</v>
+        <v>1511</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>368</v>
+        <v>1607</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>462</v>
+        <v>1712</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>520</v>
+        <v>1774</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>575</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>6</v>
+        <v>1219</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>106</v>
+        <v>1319</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>193</v>
+        <v>1418</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>279</v>
+        <v>1512</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>369</v>
+        <v>1608</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>463</v>
+        <v>1713</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>520</v>
+        <v>1775</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>575</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>6</v>
+        <v>1219</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>107</v>
+        <v>1320</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>194</v>
+        <v>1418</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>280</v>
+        <v>1512</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>370</v>
+        <v>1608</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>464</v>
+        <v>1714</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>521</v>
+        <v>1775</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>576</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>7</v>
+        <v>1219</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>108</v>
+        <v>1321</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>195</v>
+        <v>1419</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>281</v>
+        <v>1513</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>371</v>
+        <v>1609</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>465</v>
+        <v>1714</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>522</v>
+        <v>1776</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>577</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>7</v>
+        <v>1219</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>109</v>
+        <v>1322</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>196</v>
+        <v>1420</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>282</v>
+        <v>1514</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>372</v>
+        <v>1610</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>465</v>
+        <v>1714</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>523</v>
+        <v>1777</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>578</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>7</v>
+        <v>1219</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>110</v>
+        <v>1323</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>197</v>
+        <v>1421</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>283</v>
+        <v>1515</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>373</v>
+        <v>1611</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>465</v>
+        <v>1715</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>524</v>
+        <v>1778</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>579</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>7</v>
+        <v>1219</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>111</v>
+        <v>1324</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>198</v>
+        <v>1422</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>284</v>
+        <v>1516</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>374</v>
+        <v>1612</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>466</v>
+        <v>1716</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>525</v>
+        <v>1779</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>580</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>7</v>
+        <v>1219</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>112</v>
+        <v>1325</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>199</v>
+        <v>1423</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>285</v>
+        <v>1517</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>375</v>
+        <v>1613</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>467</v>
+        <v>1717</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>525</v>
+        <v>1780</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>580</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>7</v>
+        <v>1219</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>113</v>
+        <v>1326</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>200</v>
+        <v>1424</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>286</v>
+        <v>1517</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>376</v>
+        <v>1614</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>468</v>
+        <v>1718</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>525</v>
+        <v>1780</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>580</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>7</v>
+        <v>1219</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>114</v>
+        <v>1327</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>201</v>
+        <v>1425</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>287</v>
+        <v>1517</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>377</v>
-      </c>
-      <c r="F109" s="0" t="s">
-        <v>469</v>
-      </c>
+        <v>1615</v>
+      </c>
+      <c r="F109" s="0"/>
       <c r="G109" s="0" t="s">
-        <v>525</v>
+        <v>1780</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>580</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>7</v>
+        <v>1219</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>115</v>
+        <v>1328</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>202</v>
+        <v>1426</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>288</v>
+        <v>1518</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>378</v>
+        <v>1616</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>470</v>
+        <v>1719</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>525</v>
+        <v>1781</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>580</v>
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C111" s="0" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F111" s="0" t="s">
+        <v>1720</v>
+      </c>
+      <c r="G111" s="0" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H111" s="0" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C112" s="0" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E112" s="0" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F112" s="0" t="s">
+        <v>1721</v>
+      </c>
+      <c r="G112" s="0" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H112" s="0" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C113" s="0" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D113" s="0" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E113" s="0" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F113" s="0" t="s">
+        <v>1722</v>
+      </c>
+      <c r="G113" s="0" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H113" s="0" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C114" s="0" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E114" s="0" t="s">
+        <v>1620</v>
+      </c>
+      <c r="F114" s="0" t="s">
+        <v>1723</v>
+      </c>
+      <c r="G114" s="0" t="s">
+        <v>1783</v>
+      </c>
+      <c r="H114" s="0" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C115" s="0" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E115" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F115" s="0" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G115" s="0" t="s">
+        <v>1784</v>
+      </c>
+      <c r="H115" s="0" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C116" s="0" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D116" s="0" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E116" s="0" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F116" s="0" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G116" s="0" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H116" s="0" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C117" s="0" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D117" s="0" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E117" s="0" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F117" s="0" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G117" s="0" t="s">
+        <v>1786</v>
+      </c>
+      <c r="H117" s="0" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C118" s="0" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D118" s="0" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E118" s="0" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F118" s="0" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G118" s="0" t="s">
+        <v>1787</v>
+      </c>
+      <c r="H118" s="0" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C119" s="0" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D119" s="0" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F119" s="0" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G119" s="0" t="s">
+        <v>1787</v>
+      </c>
+      <c r="H119" s="0" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C120" s="0" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D120" s="0" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E120" s="0" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F120" s="0" t="s">
+        <v>1727</v>
+      </c>
+      <c r="G120" s="0" t="s">
+        <v>1787</v>
+      </c>
+      <c r="H120" s="0" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C121" s="0" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D121" s="0" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F121" s="0" t="s">
+        <v>1728</v>
+      </c>
+      <c r="G121" s="0" t="s">
+        <v>1787</v>
+      </c>
+      <c r="H121" s="0" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C122" s="0" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D122" s="0" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E122" s="0" t="s">
+        <v>1628</v>
+      </c>
+      <c r="F122" s="0" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G122" s="0" t="s">
+        <v>1787</v>
+      </c>
+      <c r="H122" s="0" t="s">
+        <v>1844</v>
       </c>
     </row>
   </sheetData>
